--- a/Data/IPParliament.xlsx
+++ b/Data/IPParliament.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,81 +472,81 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>How many houses does the Indian Parliament consist of?</t>
+          <t>Who presides over the joint sitting of Parliament?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>One</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Two</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Three</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Four</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Two</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The Indian Parliament has two houses – Lok Sabha and Rajya Sabha.</t>
+          <t>In joint sittings, the Speaker of Lok Sabha presides.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which article of the Constitution deals with the composition of the Parliament?</t>
+          <t>How many members can be nominated to the Rajya Sabha by the President?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Article 81</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Article 79 defines the structure of the Indian Parliament.</t>
+          <t>The President can nominate 12 members to Rajya Sabha from fields like art, science, etc.</t>
         </is>
       </c>
     </row>
@@ -592,4881 +592,4857 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>How many members can be nominated to the Rajya Sabha by the President?</t>
+          <t>Which article of the Constitution deals with the composition of the Parliament?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Article 81</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>The President can nominate 12 members to Rajya Sabha from fields like art, science, etc.</t>
+          <t>Article 79 defines the structure of the Indian Parliament.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who presides over the joint sitting of Parliament?</t>
+          <t>How many houses does the Indian Parliament consist of?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Two</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Three</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Four</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Two</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>In joint sittings, the Speaker of Lok Sabha presides.</t>
+          <t>The Indian Parliament has two houses – Lok Sabha and Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a function of Parliament?</t>
+          <t>In case of a deadlock between the two Houses, the President can summon a joint sitting under which article?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Law-making</t>
+          <t>Article 108</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Amending Constitution</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Controlling Executive</t>
+          <t>Article 111</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Electing President</t>
+          <t>Article 112</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Electing President</t>
+          <t>Article 108</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>President is elected by an electoral college, not Parliament alone.</t>
+          <t>Joint sitting can be called to resolve deadlock between Houses.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Money Bill can be introduced only in</t>
+          <t>The first Lok Sabha was constituted in</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Money Bills can be introduced only in Lok Sabha, as per Article 110.</t>
+          <t>The first Lok Sabha was formed in 1952 after the first general election.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which of the following is a permanent House?</t>
+          <t>Which article of the Constitution defines a Money Bill?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Article 112</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Legislative Assembly</t>
+          <t>Article 113</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Rajya Sabha is not subject to dissolution; one-third members retire every 2 years.</t>
+          <t>This article gives the definition of a Money Bill.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What is the quorum to conduct a sitting of either House of Parliament?</t>
+          <t>Which House has more power in the case of a Money Bill?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1/5th of total membership</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1/10th of total membership</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1/3rd of total membership</t>
+          <t>Both equal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Half the total strength</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1/10th of total membership</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Quorum is 1/10th of total strength of the House.</t>
+          <t>Rajya Sabha can only make recommendations on Money Bills.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The maximum gap between two sessions of Parliament cannot be more than</t>
+          <t>The Speaker of Lok Sabha is elected by</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4 months</t>
+          <t>Lok Sabha members</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Lok Sabha members</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>According to the Constitution, there must not be a gap of more than 6 months.</t>
+          <t>Speaker is elected by members of Lok Sabha from among themselves.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Speaker of Lok Sabha is elected by</t>
+          <t>The maximum gap between two sessions of Parliament cannot be more than</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lok Sabha members</t>
+          <t>4 months</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lok Sabha members</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Speaker is elected by members of Lok Sabha from among themselves.</t>
+          <t>According to the Constitution, there must not be a gap of more than 6 months.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which House has more power in the case of a Money Bill?</t>
+          <t>What is the quorum to conduct a sitting of either House of Parliament?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>1/5th of total membership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>1/10th of total membership</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Both equal</t>
+          <t>1/3rd of total membership</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Half the total strength</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>1/10th of total membership</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Rajya Sabha can only make recommendations on Money Bills.</t>
+          <t>Quorum is 1/10th of total strength of the House.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which article of the Constitution defines a Money Bill?</t>
+          <t>Which of the following is a permanent House?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Article 112</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Article 113</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Article 117</t>
-        </is>
-      </c>
+          <t>Legislative Assembly</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>This article gives the definition of a Money Bill.</t>
+          <t>Rajya Sabha is not subject to dissolution; one-third members retire every 2 years.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The first Lok Sabha was constituted in</t>
+          <t>Money Bill can be introduced only in</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>The first Lok Sabha was formed in 1952 after the first general election.</t>
+          <t>Money Bills can be introduced only in Lok Sabha, as per Article 110.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>In case of a deadlock between the two Houses, the President can summon a joint sitting under which article?</t>
+          <t>Which of the following is NOT a function of Parliament?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Article 108</t>
+          <t>Law-making</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Amending Constitution</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Article 111</t>
+          <t>Controlling Executive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Article 112</t>
+          <t>Electing President</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Article 108</t>
+          <t>Electing President</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Joint sitting can be called to resolve deadlock between Houses.</t>
+          <t>President is elected by an electoral college, not Parliament alone.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which House of Parliament can initiate impeachment of the President?</t>
+          <t>Can a non-member of Parliament become a minister?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lok Sabha only</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Rajya Sabha only</t>
+          <t>Yes, for 3 months</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Yes, for 1 year</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Both Houses can initiate impeachment independently.</t>
+          <t>He must get elected to either House within 6 months.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
+          <t>What is the current maximum strength of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>245</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>238</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>As per Article 64, Vice President is ex-officio Chairman of Rajya Sabha.</t>
+          <t>Rajya Sabha can have up to 250 members, out of which 12 are nominated.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which House of Parliament has special powers regarding creation of All-India Services?</t>
+          <t>Who decides whether a bill is a Money Bill or not?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Rajya Sabha can pass a resolution to create All-India Services.</t>
+          <t>The Speaker’s decision on Money Bill is final under Article 110.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What is the maximum tenure of Lok Sabha?</t>
+          <t>Under normal circumstances, how many sessions of Parliament are held in a year?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3 years</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Lok Sabha has a normal term of 5 years unless dissolved earlier.</t>
+          <t>Budget, Monsoon, and Winter Sessions are held annually.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Can Rajya Sabha be dissolved?</t>
+          <t>Which schedule of the Constitution deals with allocation of seats in Rajya Sabha?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes, every 6 years</t>
+          <t>First</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Yes, every 5 years</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fourth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yes, at the discretion of President</t>
+          <t>Sixth</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fourth</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
+          <t>The Fourth Schedule allocates seats in Rajya Sabha to states and UTs.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which schedule of the Constitution deals with allocation of seats in Rajya Sabha?</t>
+          <t>Can Rajya Sabha be dissolved?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>Yes, every 6 years</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Yes, every 5 years</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fourth</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sixth</t>
+          <t>Yes, at the discretion of President</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fourth</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>The Fourth Schedule allocates seats in Rajya Sabha to states and UTs.</t>
+          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Under normal circumstances, how many sessions of Parliament are held in a year?</t>
+          <t>What is the maximum tenure of Lok Sabha?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Budget, Monsoon, and Winter Sessions are held annually.</t>
+          <t>Lok Sabha has a normal term of 5 years unless dissolved earlier.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Who decides whether a bill is a Money Bill or not?</t>
+          <t>Which House of Parliament has special powers regarding creation of All-India Services?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Prime Minister</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>The Speaker’s decision on Money Bill is final under Article 110.</t>
+          <t>Rajya Sabha can pass a resolution to create All-India Services.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What is the current maximum strength of Rajya Sabha?</t>
+          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Rajya Sabha can have up to 250 members, out of which 12 are nominated.</t>
+          <t>As per Article 64, Vice President is ex-officio Chairman of Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Can a non-member of Parliament become a minister?</t>
+          <t>Which House of Parliament can initiate impeachment of the President?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Lok Sabha only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Yes, for 3 months</t>
+          <t>Rajya Sabha only</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yes, for 1 year</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>He must get elected to either House within 6 months.</t>
+          <t>Both Houses can initiate impeachment independently.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which of the following statements is true regarding the dissolution of Rajya Sabha?</t>
+          <t>Which article provides for the privileges of Parliament members?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>It is dissolved every 5 years</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>It is dissolved by the President</t>
+          <t>Article 108</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>It is dissolved by the Prime Minister</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>It cannot be dissolved</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>It cannot be dissolved</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent house and is not subject to dissolution.</t>
+          <t>This article grants MPs certain privileges and immunities.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What happens if there is a vacancy in the office of Speaker and Deputy Speaker of Lok Sabha?</t>
+          <t>Which session of Parliament is usually held from February to May?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>President presides over</t>
+          <t>Monsoon Session</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Prime Minister presides over</t>
+          <t>Winter Session</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Member appointed by President presides</t>
+          <t>Budget Session</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Any member appointed by the House presides</t>
+          <t>Special Session</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Any member appointed by the House presides</t>
+          <t>Budget Session</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>The House appoints a member to preside in absence of Speaker/Deputy Speaker.</t>
+          <t>It usually begins in February and includes the budget presentation.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What is the maximum time Rajya Sabha can hold a Money Bill?</t>
+          <t>In which schedule is the anti-defection law mentioned?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7 days</t>
+          <t>8th Schedule</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>9th Schedule</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>21 days</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>11th Schedule</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Rajya Sabha must return a Money Bill within 14 days; else it is deemed passed.</t>
+          <t>The 10th Schedule was added by the 52nd Amendment for anti-defection.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A bill becomes a law only after it is signed by</t>
+          <t>What is the term of nominated members of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>President’s assent is essential for a bill to become a law.</t>
+          <t>Like elected members, nominated members also serve for 6 years.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which of the following is not a parliamentary committee?</t>
+          <t>The motion to remove the Vice President must be introduced in</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>President’s Office</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Committee on Petitions</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Cabinet Committees are executive, not parliamentary.</t>
+          <t>Removal motion of Vice President must originate in Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The motion to remove the Vice President must be introduced in</t>
+          <t>Which of the following is not a parliamentary committee?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>President’s Office</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Committee on Petitions</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Removal motion of Vice President must originate in Rajya Sabha.</t>
+          <t>Cabinet Committees are executive, not parliamentary.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What is the term of nominated members of Rajya Sabha?</t>
+          <t>A bill becomes a law only after it is signed by</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2 years</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Like elected members, nominated members also serve for 6 years.</t>
+          <t>President’s assent is essential for a bill to become a law.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>In which schedule is the anti-defection law mentioned?</t>
+          <t>What is the maximum time Rajya Sabha can hold a Money Bill?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>8th Schedule</t>
+          <t>7 days</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9th Schedule</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>21 days</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>11th Schedule</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>The 10th Schedule was added by the 52nd Amendment for anti-defection.</t>
+          <t>Rajya Sabha must return a Money Bill within 14 days; else it is deemed passed.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which session of Parliament is usually held from February to May?</t>
+          <t>What happens if there is a vacancy in the office of Speaker and Deputy Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Monsoon Session</t>
+          <t>President presides over</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Winter Session</t>
+          <t>Prime Minister presides over</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Budget Session</t>
+          <t>Member appointed by President presides</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Special Session</t>
+          <t>Any member appointed by the House presides</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Budget Session</t>
+          <t>Any member appointed by the House presides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>It usually begins in February and includes the budget presentation.</t>
+          <t>The House appoints a member to preside in absence of Speaker/Deputy Speaker.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which article provides for the privileges of Parliament members?</t>
+          <t>Which of the following statements is true regarding the dissolution of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>It is dissolved every 5 years</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Article 108</t>
+          <t>It is dissolved by the President</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>It is dissolved by the Prime Minister</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>It cannot be dissolved</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>It cannot be dissolved</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>This article grants MPs certain privileges and immunities.</t>
+          <t>Rajya Sabha is a permanent house and is not subject to dissolution.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The first Speaker of Lok Sabha was</t>
+          <t>The Parliament can legislate on a subject in the State List if</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>G V Mavalankar</t>
+          <t>Rajya Sabha passes a resolution</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>M A Ayyangar</t>
+          <t>There is national emergency</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S Radhakrishnan</t>
+          <t>States request it</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>G V Mavalankar</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>He was the first Speaker of Lok Sabha after 1952 elections.</t>
+          <t>All these are valid conditions under which Parliament can legislate on State subjects.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>In the event of a conflict between two Houses on an ordinary bill, the mechanism used is</t>
+          <t>Which is not required to pass a Constitutional Amendment Bill?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Money Bill clause</t>
+          <t>Simple Majority</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Special Majority</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>President’s Order</t>
+          <t>Ratification by States</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Constitutional Amendment</t>
+          <t>President's assent</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Simple Majority</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Joint sitting is used to resolve deadlock on ordinary bills.</t>
+          <t>Most Constitutional Amendments require special majority, not simple majority.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>How many members of Anglo-Indian community could be nominated to Lok Sabha (before 104th Amendment)?</t>
+          <t>Which of the following motions can lead to the fall of the Council of Ministers?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Calling Attention Motion</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Adjournment Motion</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Censure Motion</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No-confidence Motion</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No-confidence Motion</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Earlier, President could nominate 2 Anglo-Indians (now discontinued after 104th Amendment).</t>
+          <t>It expresses loss of confidence in the government.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The power to summon or prorogue Parliament rests with</t>
+          <t>What is the minimum age to become a member of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>25 years</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>35 years</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>21 years</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>President summons and prorogues the Parliament on advice of Council of Ministers.</t>
+          <t>A candidate must be at least 30 years old to be elected to Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which of the following is true about Zero Hour?</t>
+          <t>Which Article authorizes Parliament to make laws on State List during national emergency?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>It is mentioned in Constitution</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>It begins at 12 noon</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>It is a procedural motion</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>It is started by Rajya Sabha</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>It begins at 12 noon</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Zero Hour starts at 12 PM and is an Indian innovation (not in Constitution).</t>
+          <t>During National Emergency, Parliament can legislate on State subjects under Article 250.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which Article authorizes Parliament to make laws on State List during national emergency?</t>
+          <t>Which of the following is true about Zero Hour?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>It is mentioned in Constitution</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>It begins at 12 noon</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>It is a procedural motion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>It is started by Rajya Sabha</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>It begins at 12 noon</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>During National Emergency, Parliament can legislate on State subjects under Article 250.</t>
+          <t>Zero Hour starts at 12 PM and is an Indian innovation (not in Constitution).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What is the minimum age to become a member of Rajya Sabha?</t>
+          <t>The power to summon or prorogue Parliament rests with</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>25 years</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>30 years</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>35 years</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>21 years</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>30 years</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>A candidate must be at least 30 years old to be elected to Rajya Sabha.</t>
+          <t>President summons and prorogues the Parliament on advice of Council of Ministers.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which of the following motions can lead to the fall of the Council of Ministers?</t>
+          <t>How many members of Anglo-Indian community could be nominated to Lok Sabha (before 104th Amendment)?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Calling Attention Motion</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Adjournment Motion</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Censure Motion</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>No-confidence Motion</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>No-confidence Motion</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>It expresses loss of confidence in the government.</t>
+          <t>Earlier, President could nominate 2 Anglo-Indians (now discontinued after 104th Amendment).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which is not required to pass a Constitutional Amendment Bill?</t>
+          <t>In the event of a conflict between two Houses on an ordinary bill, the mechanism used is</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Simple Majority</t>
+          <t>Money Bill clause</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Special Majority</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ratification by States</t>
+          <t>President’s Order</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>President's assent</t>
+          <t>Constitutional Amendment</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Simple Majority</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Most Constitutional Amendments require special majority, not simple majority.</t>
+          <t>Joint sitting is used to resolve deadlock on ordinary bills.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Parliament can legislate on a subject in the State List if</t>
+          <t>The first Speaker of Lok Sabha was</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rajya Sabha passes a resolution</t>
+          <t>G V Mavalankar</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>There is national emergency</t>
+          <t>M A Ayyangar</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>States request it</t>
+          <t>S Radhakrishnan</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>G V Mavalankar</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>All these are valid conditions under which Parliament can legislate on State subjects.</t>
+          <t>He was the first Speaker of Lok Sabha after 1952 elections.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which body examines the annual financial statement laid before Parliament?</t>
+          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>The Public Accounts Committee examines the audit reports and financial accounts.</t>
+          <t>The Speaker of the Lok Sabha presides over joint sittings.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What is the difference between adjournment and prorogation?</t>
+          <t>What is the term of a Rajya Sabha member?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>No difference</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Adjournment by President, Prorogation by Speaker</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Adjournment is for a short period, Prorogation ends session</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Adjournment ends the House</t>
+          <t>7 years</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Adjournment is for a short period, Prorogation ends session</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Adjournment is temporary; prorogation ends a session.</t>
+          <t>Rajya Sabha members have a term of 6 years, with one-third retiring every two years.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which authority decides the disqualification of MPs under anti-defection?</t>
+          <t>Which schedule of the Constitution contains the Anti-Defection Law?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>7th</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>8th</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Speaker/Chairman</t>
+          <t>9th</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Speaker/Chairman</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>The Presiding Officer decides under 10th Schedule.</t>
+          <t>The Tenth Schedule deals with provisions regarding disqualification on the grounds of defection.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Rajya Sabha can delay an ordinary bill by maximum of</t>
+          <t>What is the maximum strength of the Lok Sabha as per the Constitution?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>530</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>545</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>552</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>560</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Rajya Sabha can delay an ordinary bill for maximum 6 months.</t>
+          <t>As per Article 81, the maximum strength is 552 members.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which of the following is not a function of Parliament?</t>
+          <t>Which of the following is not a part of the Indian Parliament?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Executive appointments</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Amending Constitution</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Judicial review is the function of courts, not Parliament.</t>
+          <t>The Supreme Court is part of the Judiciary, not the Parliament.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which of the following is not a part of the Indian Parliament?</t>
+          <t>Which of the following is not a function of Parliament?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Executive appointments</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Amending Constitution</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>The Supreme Court is part of the Judiciary, not the Parliament.</t>
+          <t>Judicial review is the function of courts, not Parliament.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>What is the maximum strength of the Lok Sabha as per the Constitution?</t>
+          <t>The Rajya Sabha can delay an ordinary bill by maximum of</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>1 month</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>As per Article 81, the maximum strength is 552 members.</t>
+          <t>Rajya Sabha can delay an ordinary bill for maximum 6 months.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which schedule of the Constitution contains the Anti-Defection Law?</t>
+          <t>Which authority decides the disqualification of MPs under anti-defection?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8th</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>Speaker/Chairman</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>Speaker/Chairman</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>The Tenth Schedule deals with provisions regarding disqualification on the grounds of defection.</t>
+          <t>The Presiding Officer decides under 10th Schedule.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What is the term of a Rajya Sabha member?</t>
+          <t>What is the difference between adjournment and prorogation?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>No difference</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Adjournment by President, Prorogation by Speaker</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Adjournment is for a short period, Prorogation ends session</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>7 years</t>
+          <t>Adjournment ends the House</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Adjournment is for a short period, Prorogation ends session</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Rajya Sabha members have a term of 6 years, with one-third retiring every two years.</t>
+          <t>Adjournment is temporary; prorogation ends a session.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
+          <t>Which body examines the annual financial statement laid before Parliament?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>The Speaker of the Lok Sabha presides over joint sittings.</t>
+          <t>The Public Accounts Committee examines the audit reports and financial accounts.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which Article mentions the composition of the Rajya Sabha?</t>
+          <t>Who acts as the pro tem Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Longest-serving MP</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Article 81</t>
+          <t>Senior-most member</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Article 82</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Article 83</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Senior-most member</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Article 80 of the Constitution deals with the composition of Rajya Sabha.</t>
+          <t>The senior-most member is appointed to conduct the first meeting until Speaker is elected.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Money Bills can be introduced only in which House?</t>
+          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Only Lok Sabha can introduce a Money Bill as per Article 110.</t>
+          <t>The Vice President of India is the ex-officio Chairman of Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The quorum for a meeting of either House of Parliament is?</t>
+          <t>Which of the following is not a function of Parliament?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1/5th</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1/4th</t>
+          <t>Amending the Constitution</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1/6th</t>
+          <t>Electing the President</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1/10th</t>
+          <t>Enforcing laws</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1/10th</t>
+          <t>Enforcing laws</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>The minimum number of members required to hold a meeting is 1/10th of the total strength.</t>
+          <t>Enforcing laws is the function of the executive.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The power to summon or prorogue the Parliament rests with?</t>
+          <t>Can the Rajya Sabha be dissolved?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Yes, after 6 years</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Yes, by the President</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Only in emergency</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>The President summons and prorogues Parliament sessions.</t>
+          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which House is considered the Council of States?</t>
+          <t>Who decides whether a bill is a Money Bill or not?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vidhan Sabha</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Rajya Sabha represents the states and is called the Council of States.</t>
+          <t>As per Article 110, the Speaker's decision is final.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Who decides whether a bill is a Money Bill or not?</t>
+          <t>Which House is considered the Council of States?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Finance Minister</t>
-        </is>
-      </c>
+          <t>Vidhan Sabha</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>As per Article 110, the Speaker's decision is final.</t>
+          <t>Rajya Sabha represents the states and is called the Council of States.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Can the Rajya Sabha be dissolved?</t>
+          <t>The power to summon or prorogue the Parliament rests with?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Yes, after 6 years</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Yes, by the President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Only in emergency</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
+          <t>The President summons and prorogues Parliament sessions.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which of the following is not a function of Parliament?</t>
+          <t>The quorum for a meeting of either House of Parliament is?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>1/5th</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Amending the Constitution</t>
+          <t>1/4th</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Electing the President</t>
+          <t>1/6th</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Enforcing laws</t>
+          <t>1/10th</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Enforcing laws</t>
+          <t>1/10th</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Enforcing laws is the function of the executive.</t>
+          <t>The minimum number of members required to hold a meeting is 1/10th of the total strength.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
+          <t>Money Bills can be introduced only in which House?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Vice President</t>
-        </is>
-      </c>
+          <t>Either House</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>The Vice President of India is the ex-officio Chairman of Rajya Sabha.</t>
+          <t>Only Lok Sabha can introduce a Money Bill as per Article 110.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Who acts as the pro tem Speaker of Lok Sabha?</t>
+          <t>Which Article mentions the composition of the Rajya Sabha?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Longest-serving MP</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Senior-most member</t>
+          <t>Article 81</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 82</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Article 83</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Senior-most member</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>The senior-most member is appointed to conduct the first meeting until Speaker is elected.</t>
+          <t>Article 80 of the Constitution deals with the composition of Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which of the following is NOT true about Rajya Sabha?</t>
+          <t>The first sitting of the Constituent Assembly took place in which year?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>It is a permanent House</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>It has equal powers with Lok Sabha on Money Bills</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>It represents states</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>It has 250 members</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>It has equal powers with Lok Sabha on Money Bills</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Rajya Sabha has limited role in Money Bills.</t>
+          <t>The Constituent Assembly first met on 9 December 1946.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The maximum number of nominated members in Rajya Sabha is?</t>
+          <t>Which Article empowers the Parliament to make laws on State List during emergency?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Article 248</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>The President can nominate 12 members with special knowledge in fields like art, literature, etc.</t>
+          <t>Parliament can legislate on state subjects during National Emergency under Article 250.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>In case of deadlock between two Houses on a bill, who summons the joint sitting?</t>
+          <t>What is the tenure of the Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Till next election</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Till he/she resigns or removed</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Till he/she resigns or removed</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>President summons a joint session to resolve the deadlock.</t>
+          <t>Speaker holds office until removed or resignation, even after dissolution.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Who can introduce an ordinary bill in Parliament?</t>
+          <t>Which Committee examines the report of the Comptroller and Auditor General (CAG)?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Only Minister</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Only MP from ruling party</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Privileges Committee</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Only Lok Sabha MP</t>
+          <t>Business Advisory Committee</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Ordinary Bills can be introduced by any MP.</t>
+          <t>PAC examines CAG reports and ensures public money is spent properly.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>In which year was the Parliament House of India inaugurated?</t>
+          <t>Which constitutional amendment lowered the voting age from 21 to 18?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>42nd</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>44th</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>61st</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>52nd</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>61st</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>The current Parliament House was inaugurated in 1927 by Lord Irwin.</t>
+          <t>The 61st Amendment Act, 1989, reduced the voting age.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which constitutional amendment lowered the voting age from 21 to 18?</t>
+          <t>In which year was the Parliament House of India inaugurated?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>42nd</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>44th</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>61st</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>52nd</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>61st</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>The 61st Amendment Act, 1989, reduced the voting age.</t>
+          <t>The current Parliament House was inaugurated in 1927 by Lord Irwin.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which Committee examines the report of the Comptroller and Auditor General (CAG)?</t>
+          <t>Who can introduce an ordinary bill in Parliament?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>Only Minister</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>Only MP from ruling party</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Privileges Committee</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Business Advisory Committee</t>
+          <t>Only Lok Sabha MP</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>PAC examines CAG reports and ensures public money is spent properly.</t>
+          <t>Ordinary Bills can be introduced by any MP.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>What is the tenure of the Speaker of Lok Sabha?</t>
+          <t>In case of deadlock between two Houses on a bill, who summons the joint sitting?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Till next election</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Till he/she resigns or removed</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Till he/she resigns or removed</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Speaker holds office until removed or resignation, even after dissolution.</t>
+          <t>President summons a joint session to resolve the deadlock.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which Article empowers the Parliament to make laws on State List during emergency?</t>
+          <t>The maximum number of nominated members in Rajya Sabha is?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Article 248</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Parliament can legislate on state subjects during National Emergency under Article 250.</t>
+          <t>The President can nominate 12 members with special knowledge in fields like art, literature, etc.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The first sitting of the Constituent Assembly took place in which year?</t>
+          <t>Which of the following is NOT true about Rajya Sabha?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>It is a permanent House</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>It has equal powers with Lok Sabha on Money Bills</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>It represents states</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>It has 250 members</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>It has equal powers with Lok Sabha on Money Bills</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>The Constituent Assembly first met on 9 December 1946.</t>
+          <t>Rajya Sabha has limited role in Money Bills.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which Article allows the Parliament to make laws on a matter in the State List under national interest?</t>
+          <t>Who is the custodian of the Lok Sabha?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Rajya Sabha can authorize Parliament to legislate on State List in national interest.</t>
+          <t>The Speaker is the guardian and controller of Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Who can disqualify a Member of Parliament on grounds of defection?</t>
+          <t>Which of the following is NOT a function of the Estimates Committee?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Suggesting economic improvements</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Examining estimates in Budget</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Speaker or Chairman</t>
+          <t>Examining CAG reports</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Ensuring efficient allocation</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Speaker or Chairman</t>
+          <t>Examining CAG reports</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>They decide disqualification under the 10th Schedule.</t>
+          <t>That's the job of Public Accounts Committee, not Estimates Committee.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which of the following statements is correct regarding Money Bill?</t>
+          <t>What happens if there is a deadlock on a Constitutional Amendment Bill?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>It needs approval of Rajya Sabha</t>
+          <t>Joint Sitting is held</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Rajya Sabha can reject it</t>
+          <t>President decides</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rajya Sabha can suggest amendments</t>
+          <t>Lok Sabha prevails</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rajya Sabha can amend it</t>
+          <t>Bill fails</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rajya Sabha can suggest amendments</t>
+          <t>Bill fails</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Rajya Sabha can only suggest, not amend or reject it.</t>
+          <t>There is no provision for joint sitting on Constitutional Amendments.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>How many types of major parliamentary committees exist in India?</t>
+          <t>Which Article deals with the procedure in financial matters like Budget?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Article 109</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Article 112</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Standing and Ad-hoc are the two main types.</t>
+          <t>It governs financial bills other than money bills.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which of the following motions needs the support of at least 50 members to be admitted in Lok Sabha?</t>
+          <t>How many members can the President nominate to Lok Sabha from Anglo-Indian community (until removed)?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>No-confidence motion</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Censure motion</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Privilege motion</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>It needs support of 50 members for admission.</t>
+          <t>Till the 104th Amendment (2020), President could nominate 2 Anglo-Indians.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>How many members can the President nominate to Lok Sabha from Anglo-Indian community (until removed)?</t>
+          <t>Which of the following motions needs the support of at least 50 members to be admitted in Lok Sabha?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No-confidence motion</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Censure motion</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Privilege motion</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Till the 104th Amendment (2020), President could nominate 2 Anglo-Indians.</t>
+          <t>It needs support of 50 members for admission.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which Article deals with the procedure in financial matters like Budget?</t>
+          <t>How many types of major parliamentary committees exist in India?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Article 109</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Article 112</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>It governs financial bills other than money bills.</t>
+          <t>Standing and Ad-hoc are the two main types.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>What happens if there is a deadlock on a Constitutional Amendment Bill?</t>
+          <t>Which of the following statements is correct regarding Money Bill?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Joint Sitting is held</t>
+          <t>It needs approval of Rajya Sabha</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>President decides</t>
+          <t>Rajya Sabha can reject it</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lok Sabha prevails</t>
+          <t>Rajya Sabha can suggest amendments</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bill fails</t>
+          <t>Rajya Sabha can amend it</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bill fails</t>
+          <t>Rajya Sabha can suggest amendments</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>There is no provision for joint sitting on Constitutional Amendments.</t>
+          <t>Rajya Sabha can only suggest, not amend or reject it.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a function of the Estimates Committee?</t>
+          <t>Who can disqualify a Member of Parliament on grounds of defection?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Suggesting economic improvements</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Examining estimates in Budget</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Examining CAG reports</t>
+          <t>Speaker or Chairman</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ensuring efficient allocation</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Examining CAG reports</t>
+          <t>Speaker or Chairman</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>That's the job of Public Accounts Committee, not Estimates Committee.</t>
+          <t>They decide disqualification under the 10th Schedule.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Who is the custodian of the Lok Sabha?</t>
+          <t>Which Article allows the Parliament to make laws on a matter in the State List under national interest?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>The Speaker is the guardian and controller of Lok Sabha.</t>
+          <t>Rajya Sabha can authorize Parliament to legislate on State List in national interest.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>In which case did the Supreme Court rule that Parliament cannot alter the Basic Structure?</t>
+          <t>Which provision ensures that Parliament remains sovereign in making laws?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Minerva Mills v. Union of India</t>
+          <t>Doctrine of pith and substance</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Golak Nath v. State of Punjab</t>
+          <t>Basic structure</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati v. State of Kerala</t>
+          <t>Separation of powers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SR Bommai v. Union of India</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati v. State of Kerala</t>
+          <t>Doctrine of pith and substance</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>This judgment introduced the Basic Structure doctrine.</t>
+          <t>It gives Parliament flexibility in legislative matters.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which committee is called the “watchdog of public purse”?</t>
+          <t>Who can introduce a bill for Constitutional Amendment?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>Only Ministers</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>Only Lok Sabha MP</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Committee on Subordinate Legislation</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Committee on Public Undertakings</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>It ensures accountability in public spending.</t>
+          <t>Both Ministers and private members can introduce Constitutional Amendments.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a type of bill in Indian Parliament?</t>
+          <t>What is the quorum of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Appropriation Bill</t>
+          <t>15 members</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>1/6th of total</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>1/10th of total</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Judicial Bill</t>
+          <t>50 members</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Judicial Bill</t>
+          <t>1/10th of total</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>There’s no such category; only legislative, money, financial bills exist.</t>
+          <t>Minimum 1/10th of the total strength is required to conduct business.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>How many readings does a bill go through in the Parliament?</t>
+          <t>In which year was the Anti-Defection Law added to the Constitution?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Each House of Parliament conducts 3 readings: introduction, consideration, and passing.</t>
+          <t>It was added through the 52nd Amendment in 1985.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which Article empowers Parliament to create new states?</t>
+          <t>What is the maximum gap allowed between two parliamentary sessions?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Article 2</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>4 months</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Article 4</t>
+          <t>5 months</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Article 5</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>It gives Parliament power to create or alter state boundaries.</t>
+          <t>Parliament must meet at least once every six months.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>What is the maximum gap allowed between two parliamentary sessions?</t>
+          <t>Which Article empowers Parliament to create new states?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Article 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>4 months</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>5 months</t>
+          <t>Article 4</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Article 5</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Parliament must meet at least once every six months.</t>
+          <t>It gives Parliament power to create or alter state boundaries.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>In which year was the Anti-Defection Law added to the Constitution?</t>
+          <t>How many readings does a bill go through in the Parliament?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>It was added through the 52nd Amendment in 1985.</t>
+          <t>Each House of Parliament conducts 3 readings: introduction, consideration, and passing.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>What is the quorum of Rajya Sabha?</t>
+          <t>Which of the following is NOT a type of bill in Indian Parliament?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>15 members</t>
+          <t>Appropriation Bill</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1/6th of total</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1/10th of total</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>50 members</t>
+          <t>Judicial Bill</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1/10th of total</t>
+          <t>Judicial Bill</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Minimum 1/10th of the total strength is required to conduct business.</t>
+          <t>There’s no such category; only legislative, money, financial bills exist.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Who can introduce a bill for Constitutional Amendment?</t>
+          <t>Which committee is called the “watchdog of public purse”?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Only Ministers</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Only Lok Sabha MP</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Committee on Subordinate Legislation</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Committee on Public Undertakings</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Both Ministers and private members can introduce Constitutional Amendments.</t>
+          <t>It ensures accountability in public spending.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which provision ensures that Parliament remains sovereign in making laws?</t>
+          <t>In which case did the Supreme Court rule that Parliament cannot alter the Basic Structure?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Doctrine of pith and substance</t>
+          <t>Minerva Mills v. Union of India</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Basic structure</t>
+          <t>Golak Nath v. State of Punjab</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>Keshavananda Bharati v. State of Kerala</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>SR Bommai v. Union of India</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Doctrine of pith and substance</t>
+          <t>Keshavananda Bharati v. State of Kerala</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>It gives Parliament flexibility in legislative matters.</t>
+          <t>This judgment introduced the Basic Structure doctrine.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What is the maximum number of members in Rajya Sabha from a single state?</t>
+          <t>Which article empowers the Parliament to make laws on State List under certain circumstances?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>Article 263</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>Article 312</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Uttar Pradesh sends the highest number (31) to Rajya Sabha.</t>
+          <t>Under Article 249, Rajya Sabha can pass a resolution allowing Parliament to legislate on State List.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Who can introduce a Private Member Bill?</t>
+          <t>How many times can the President summon Parliament in a year at minimum?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Only opposition MPs</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Any non-minister MP</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Only ruling party MP</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Only nominated MPs</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Any non-minister MP</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Private Member Bills are introduced by MPs who are not Ministers.</t>
+          <t>There must be at least two sessions in a year as per Article 85.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which motion is used to express disapproval of a specific policy of the government?</t>
+          <t>Which House of Parliament is considered more powerful in terms of money matters?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>No-confidence motion</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Censure motion</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>Both equal</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cut motion</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Censure motion</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>It expresses strong disapproval of a specific policy.</t>
+          <t>Money Bills can only be introduced and passed in the Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which Article provides for the privileges of Parliament?</t>
+          <t>What is the quorum to constitute a meeting of the Lok Sabha?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Article 104</t>
+          <t>1/2 of total members</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>1/10 of total members</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Article 106</t>
+          <t>1/5 of total members</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>1/4 of total members</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>1/10 of total members</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>It provides for the powers, privileges and immunities of Parliament and its members.</t>
+          <t>Quorum is the minimum number of members required to hold a sitting.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which of the following statements is true regarding Zero Hour?</t>
+          <t>Which Schedule of the Constitution contains provisions relating to disqualification on the grounds of defection?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>It is mentioned in Constitution</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>It starts at 11 AM</t>
+          <t>9th Schedule</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>It starts after lunch</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>It is a parliamentary convention</t>
+          <t>12th Schedule</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>It is a parliamentary convention</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Zero Hour is not in the rulebook, it's a practice started in 1962.</t>
+          <t>10th Schedule deals with anti-defection law as added by the 52nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Which Schedule of the Constitution contains provisions relating to disqualification on the grounds of defection?</t>
+          <t>Which of the following statements is true regarding Zero Hour?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>It is mentioned in Constitution</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>9th Schedule</t>
+          <t>It starts at 11 AM</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>It starts after lunch</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>12th Schedule</t>
+          <t>It is a parliamentary convention</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>It is a parliamentary convention</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>10th Schedule deals with anti-defection law as added by the 52nd Amendment.</t>
+          <t>Zero Hour is not in the rulebook, it's a practice started in 1962.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>What is the quorum to constitute a meeting of the Lok Sabha?</t>
+          <t>Which Article provides for the privileges of Parliament?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1/2 of total members</t>
+          <t>Article 104</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1/10 of total members</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1/5 of total members</t>
+          <t>Article 106</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1/4 of total members</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1/10 of total members</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Quorum is the minimum number of members required to hold a sitting.</t>
+          <t>It provides for the powers, privileges and immunities of Parliament and its members.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Which House of Parliament is considered more powerful in terms of money matters?</t>
+          <t>Which motion is used to express disapproval of a specific policy of the government?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>No-confidence motion</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Censure motion</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Both equal</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Cut motion</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Censure motion</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Money Bills can only be introduced and passed in the Lok Sabha.</t>
+          <t>It expresses strong disapproval of a specific policy.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>How many times can the President summon Parliament in a year at minimum?</t>
+          <t>Who can introduce a Private Member Bill?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Only opposition MPs</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Any non-minister MP</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Only ruling party MP</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Only nominated MPs</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Any non-minister MP</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>There must be at least two sessions in a year as per Article 85.</t>
+          <t>Private Member Bills are introduced by MPs who are not Ministers.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Which article empowers the Parliament to make laws on State List under certain circumstances?</t>
+          <t>What is the maximum number of members in Rajya Sabha from a single state?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Article 263</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Article 312</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Under Article 249, Rajya Sabha can pass a resolution allowing Parliament to legislate on State List.</t>
+          <t>Uttar Pradesh sends the highest number (31) to Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>What is the maximum time limit within which Parliament must approve a Money Bill after it is introduced?</t>
+          <t>Who decides whether a Bill is a Money Bill or not?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>75 days</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Money Bill must be passed within 14 days by both Houses.</t>
+          <t>Speaker’s decision is final under Article 110.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>In case of a deadlock between the two Houses, how is the issue resolved?</t>
+          <t>Which of the following motions is NOT related to financial matters?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>President’s Rule</t>
+          <t>Cut Motion</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Prime Minister’s veto</t>
+          <t>Adjournment Motion</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Appropriation Bill</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Finance Bill</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Adjournment Motion</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>A joint sitting of Parliament is called under Article 108.</t>
+          <t>It is used to draw attention to urgent matters, not financial matters.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which of the following statements is incorrect regarding the Speaker of Lok Sabha?</t>
+          <t>What is the tenure of the members of the Rajya Sabha?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>He/she can vote in first instance</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>He/she is elected from among Lok Sabha members</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>He/she can disqualify a member under anti-defection law</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>He/she is subordinate to the President</t>
+          <t>Till dissolved</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>He/she is subordinate to the President</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Speaker is not subordinate to anyone; he is the constitutional authority.</t>
+          <t>One-third members retire every 2 years.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Which of the following bills cannot be introduced in Rajya Sabha?</t>
+          <t>Which House of Parliament is not subject to dissolution?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Constitution Amendment Bill</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Financial Bill (Type II)</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Only Lok Sabha can introduce a Money Bill.</t>
+          <t>Rajya Sabha is a permanent House, not subject to dissolution.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>The concept of Parliamentary Privileges in India is taken from which country?</t>
+          <t>The term ‘Zero Hour’ refers to</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>First hour after lunch</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Time before Question Hour</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Time immediately after Question Hour</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Time after adjournment</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Time immediately after Question Hour</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>India borrowed Parliamentary Privileges from the British system.</t>
+          <t>Zero Hour is an Indian innovation, used to raise urgent matters.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>The term ‘Zero Hour’ refers to</t>
+          <t>The concept of Parliamentary Privileges in India is taken from which country?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>First hour after lunch</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Time before Question Hour</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Time immediately after Question Hour</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Time after adjournment</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Time immediately after Question Hour</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Zero Hour is an Indian innovation, used to raise urgent matters.</t>
+          <t>India borrowed Parliamentary Privileges from the British system.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Which House of Parliament is not subject to dissolution?</t>
+          <t>Which of the following bills cannot be introduced in Rajya Sabha?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Constitution Amendment Bill</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Financial Bill (Type II)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent House, not subject to dissolution.</t>
+          <t>Only Lok Sabha can introduce a Money Bill.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>What is the tenure of the members of the Rajya Sabha?</t>
+          <t>Which of the following statements is incorrect regarding the Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>He/she can vote in first instance</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>He/she is elected from among Lok Sabha members</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>He/she can disqualify a member under anti-defection law</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Till dissolved</t>
+          <t>He/she is subordinate to the President</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>He/she is subordinate to the President</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>One-third members retire every 2 years.</t>
+          <t>Speaker is not subordinate to anyone; he is the constitutional authority.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Which of the following motions is NOT related to financial matters?</t>
+          <t>In case of a deadlock between the two Houses, how is the issue resolved?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cut Motion</t>
+          <t>President’s Rule</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Adjournment Motion</t>
+          <t>Prime Minister’s veto</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Appropriation Bill</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Finance Bill</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Adjournment Motion</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>It is used to draw attention to urgent matters, not financial matters.</t>
+          <t>A joint sitting of Parliament is called under Article 108.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Who decides whether a Bill is a Money Bill or not?</t>
+          <t>What is the maximum time limit within which Parliament must approve a Money Bill after it is introduced?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+          <t>75 days</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Speaker’s decision is final under Article 110.</t>
+          <t>Money Bill must be passed within 14 days by both Houses.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Which article empowers Parliament to create new states?</t>
+          <t>Which article mentions the composition of Parliament?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Article 2</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Article 1</t>
+          <t>Article 81</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Article 5</t>
+          <t>Article 82</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Parliament can form new states or alter existing ones.</t>
+          <t>Article 79 states that Parliament consists of President, Lok Sabha, and Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>What is the maximum gap between two sessions of Parliament?</t>
+          <t>Which motion is used to reduce the amount of a demand for grant?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Cut Motion</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>4 months</t>
+          <t>No-Confidence Motion</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Censure Motion</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Privilege Motion</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Cut Motion</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>There must not be more than a six-month gap between two sessions.</t>
+          <t>Cut motions are used to oppose specific provisions in the budget.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Under which article can Parliament punish a person for breach of privilege?</t>
+          <t>Which of the following is NOT a part of Parliament?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Article 107</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Article 118</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>It includes the powers and privileges of Parliament members.</t>
+          <t>He is part of Judiciary, not Legislature.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>The first hour of every parliamentary sitting is reserved for:</t>
+          <t>Which body recommends disqualification of members on grounds of defection?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Debate</t>
+          <t>Speaker/Chairman</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Question Hour</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Private member bill</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Question Hour</t>
+          <t>Speaker/Chairman</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>It is devoted to questions and answers.</t>
+          <t>Presiding officer decides on disqualification under anti-defection law.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
+          <t>Which of the following statements is true about Private Member’s Bill?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Introduced only by ministers</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Introduced only in Lok Sabha</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Introduced by any MP not a minister</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Requires President’s assent first</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Introduced by any MP not a minister</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>He presides over joint sittings under Article 108.</t>
+          <t>Private Members are MPs who are not part of the executive.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Which of the following statements is true about Private Member’s Bill?</t>
+          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Introduced only by ministers</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Introduced only in Lok Sabha</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Introduced by any MP not a minister</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Requires President’s assent first</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Introduced by any MP not a minister</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Private Members are MPs who are not part of the executive.</t>
+          <t>He presides over joint sittings under Article 108.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which body recommends disqualification of members on grounds of defection?</t>
+          <t>The first hour of every parliamentary sitting is reserved for:</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Speaker/Chairman</t>
+          <t>Debate</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Question Hour</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Private member bill</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Speaker/Chairman</t>
+          <t>Question Hour</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Presiding officer decides on disqualification under anti-defection law.</t>
+          <t>It is devoted to questions and answers.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a part of Parliament?</t>
+          <t>Under which article can Parliament punish a person for breach of privilege?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Article 107</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Article 118</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>He is part of Judiciary, not Legislature.</t>
+          <t>It includes the powers and privileges of Parliament members.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Which motion is used to reduce the amount of a demand for grant?</t>
+          <t>What is the maximum gap between two sessions of Parliament?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cut Motion</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>No-Confidence Motion</t>
+          <t>4 months</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Censure Motion</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Privilege Motion</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cut Motion</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Cut motions are used to oppose specific provisions in the budget.</t>
+          <t>There must not be more than a six-month gap between two sessions.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which article mentions the composition of Parliament?</t>
+          <t>Which article empowers Parliament to create new states?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>Article 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Article 81</t>
+          <t>Article 1</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Article 82</t>
+          <t>Article 5</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Article 79 states that Parliament consists of President, Lok Sabha, and Rajya Sabha.</t>
+          <t>Parliament can form new states or alter existing ones.</t>
         </is>
       </c>
     </row>

--- a/Data/IPParliament.xlsx
+++ b/Data/IPParliament.xlsx
@@ -472,837 +472,841 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Who presides over the joint sitting of Parliament?</t>
+          <t>Who decides whether a bill is a Money Bill or not?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Finance Minister</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Speaker of Lok Sabha</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Lok Sabha Speaker</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Vice President</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>In joint sittings, the Speaker of Lok Sabha presides.</t>
+          <t>The Speaker’s decision on Money Bill is final under Article 110.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>How many members can be nominated to the Rajya Sabha by the President?</t>
+          <t>Which provision ensures that Parliament remains sovereign in making laws?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Doctrine of pith and substance</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Basic structure</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Separation of powers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Doctrine of pith and substance</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The President can nominate 12 members to Rajya Sabha from fields like art, science, etc.</t>
+          <t>It gives Parliament flexibility in legislative matters.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The maximum strength of the Lok Sabha is</t>
+          <t>Which of the following is NOT a part of Parliament?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>According to Article 81, the Lok Sabha can have up to 552 members.</t>
+          <t>He is part of Judiciary, not Legislature.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which article of the Constitution deals with the composition of the Parliament?</t>
+          <t>Which Article authorizes Parliament to make laws on State List during national emergency?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Article 81</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Article 79 defines the structure of the Indian Parliament.</t>
+          <t>During National Emergency, Parliament can legislate on State subjects under Article 250.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>How many houses does the Indian Parliament consist of?</t>
+          <t>What is the tenure of the Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>One</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Two</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Three</t>
+          <t>Till next election</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Four</t>
+          <t>Till he/she resigns or removed</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Two</t>
+          <t>Till he/she resigns or removed</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>The Indian Parliament has two houses – Lok Sabha and Rajya Sabha.</t>
+          <t>Speaker holds office until removed or resignation, even after dissolution.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>In case of a deadlock between the two Houses, the President can summon a joint sitting under which article?</t>
+          <t>What happens if there is a vacancy in the office of Speaker and Deputy Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Article 108</t>
+          <t>President presides over</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Prime Minister presides over</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Article 111</t>
+          <t>Member appointed by President presides</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Article 112</t>
+          <t>Any member appointed by the House presides</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Article 108</t>
+          <t>Any member appointed by the House presides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Joint sitting can be called to resolve deadlock between Houses.</t>
+          <t>The House appoints a member to preside in absence of Speaker/Deputy Speaker.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The first Lok Sabha was constituted in</t>
+          <t>Which of the following is NOT a function of the Estimates Committee?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Suggesting economic improvements</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>Examining estimates in Budget</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>Examining CAG reports</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Ensuring efficient allocation</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>Examining CAG reports</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>The first Lok Sabha was formed in 1952 after the first general election.</t>
+          <t>That's the job of Public Accounts Committee, not Estimates Committee.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which article of the Constitution defines a Money Bill?</t>
+          <t>Which of the following statements is true about Private Member’s Bill?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Introduced only by ministers</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Article 112</t>
+          <t>Introduced only in Lok Sabha</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Article 113</t>
+          <t>Introduced by any MP not a minister</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>Requires President’s assent first</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Introduced by any MP not a minister</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>This article gives the definition of a Money Bill.</t>
+          <t>Private Members are MPs who are not part of the executive.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which House has more power in the case of a Money Bill?</t>
+          <t>Which schedule of the Constitution contains the Anti-Defection Law?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>7th</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>8th</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Both equal</t>
+          <t>9th</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Rajya Sabha can only make recommendations on Money Bills.</t>
+          <t>The Tenth Schedule deals with provisions regarding disqualification on the grounds of defection.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Speaker of Lok Sabha is elected by</t>
+          <t>In which year was the Parliament House of India inaugurated?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lok Sabha members</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lok Sabha members</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Speaker is elected by members of Lok Sabha from among themselves.</t>
+          <t>The current Parliament House was inaugurated in 1927 by Lord Irwin.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The maximum gap between two sessions of Parliament cannot be more than</t>
+          <t>Can a non-member of Parliament become a minister?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4 months</t>
+          <t>Yes, for 3 months</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Yes, for 1 year</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>According to the Constitution, there must not be a gap of more than 6 months.</t>
+          <t>He must get elected to either House within 6 months.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What is the quorum to conduct a sitting of either House of Parliament?</t>
+          <t>Which of the following statements is correct regarding Money Bill?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1/5th of total membership</t>
+          <t>It needs approval of Rajya Sabha</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1/10th of total membership</t>
+          <t>Rajya Sabha can reject it</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1/3rd of total membership</t>
+          <t>Rajya Sabha can suggest amendments</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Half the total strength</t>
+          <t>Rajya Sabha can amend it</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1/10th of total membership</t>
+          <t>Rajya Sabha can suggest amendments</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Quorum is 1/10th of total strength of the House.</t>
+          <t>Rajya Sabha can only suggest, not amend or reject it.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which of the following is a permanent House?</t>
+          <t>The power to summon or prorogue the Parliament rests with?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Legislative Assembly</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>Vice President</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Rajya Sabha is not subject to dissolution; one-third members retire every 2 years.</t>
+          <t>The President summons and prorogues Parliament sessions.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Money Bill can be introduced only in</t>
+          <t>Which of the following is not a function of Parliament?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Amending the Constitution</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Electing the President</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Enforcing laws</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Enforcing laws</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Money Bills can be introduced only in Lok Sabha, as per Article 110.</t>
+          <t>Enforcing laws is the function of the executive.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a function of Parliament?</t>
+          <t>What is the maximum strength of the Lok Sabha as per the Constitution?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Law-making</t>
+          <t>530</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Amending Constitution</t>
+          <t>545</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Controlling Executive</t>
+          <t>552</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Electing President</t>
+          <t>560</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Electing President</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>President is elected by an electoral college, not Parliament alone.</t>
+          <t>As per Article 81, the maximum strength is 552 members.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Can a non-member of Parliament become a minister?</t>
+          <t>Who acts as the pro tem Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Longest-serving MP</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Yes, for 3 months</t>
+          <t>Senior-most member</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yes, for 1 year</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>Senior-most member</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>He must get elected to either House within 6 months.</t>
+          <t>The senior-most member is appointed to conduct the first meeting until Speaker is elected.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What is the current maximum strength of Rajya Sabha?</t>
+          <t>Which of the following is NOT true about Rajya Sabha?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>It is a permanent House</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>It has equal powers with Lok Sabha on Money Bills</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>It represents states</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>It has 250 members</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>It has equal powers with Lok Sabha on Money Bills</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Rajya Sabha can have up to 250 members, out of which 12 are nominated.</t>
+          <t>Rajya Sabha has limited role in Money Bills.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Who decides whether a bill is a Money Bill or not?</t>
+          <t>The first sitting of the Constituent Assembly took place in which year?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>The Speaker’s decision on Money Bill is final under Article 110.</t>
+          <t>The Constituent Assembly first met on 9 December 1946.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Under normal circumstances, how many sessions of Parliament are held in a year?</t>
+          <t>Which is not required to pass a Constitutional Amendment Bill?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Simple Majority</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Special Majority</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Ratification by States</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>President's assent</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Simple Majority</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Budget, Monsoon, and Winter Sessions are held annually.</t>
+          <t>Most Constitutional Amendments require special majority, not simple majority.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which schedule of the Constitution deals with allocation of seats in Rajya Sabha?</t>
+          <t>In which schedule is the anti-defection law mentioned?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>8th Schedule</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>9th Schedule</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fourth</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sixth</t>
+          <t>11th Schedule</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fourth</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>The Fourth Schedule allocates seats in Rajya Sabha to states and UTs.</t>
+          <t>The 10th Schedule was added by the 52nd Amendment for anti-defection.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Can Rajya Sabha be dissolved?</t>
+          <t>The term ‘Zero Hour’ refers to</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes, every 6 years</t>
+          <t>First hour after lunch</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Yes, every 5 years</t>
+          <t>Time before Question Hour</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Time immediately after Question Hour</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yes, at the discretion of President</t>
+          <t>Time after adjournment</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Time immediately after Question Hour</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
+          <t>Zero Hour is an Indian innovation, used to raise urgent matters.</t>
         </is>
       </c>
     </row>
@@ -1312,1223 +1316,1223 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What is the maximum tenure of Lok Sabha?</t>
+          <t>Who can introduce an ordinary bill in Parliament?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3 years</t>
+          <t>Only Minister</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Only MP from ruling party</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Only Lok Sabha MP</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Lok Sabha has a normal term of 5 years unless dissolved earlier.</t>
+          <t>Ordinary Bills can be introduced by any MP.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which House of Parliament has special powers regarding creation of All-India Services?</t>
+          <t>Which of the following is not a part of the Indian Parliament?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Rajya Sabha</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Lok Sabha</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Rajya Sabha</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Supreme Court</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Rajya Sabha can pass a resolution to create All-India Services.</t>
+          <t>The Supreme Court is part of the Judiciary, not the Parliament.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
+          <t>What is the quorum to constitute a meeting of the Lok Sabha?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>1/2 of total members</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>1/10 of total members</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>1/5 of total members</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>1/4 of total members</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>1/10 of total members</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>As per Article 64, Vice President is ex-officio Chairman of Rajya Sabha.</t>
+          <t>Quorum is the minimum number of members required to hold a sitting.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which House of Parliament can initiate impeachment of the President?</t>
+          <t>What is the difference between adjournment and prorogation?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lok Sabha only</t>
+          <t>No difference</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Rajya Sabha only</t>
+          <t>Adjournment by President, Prorogation by Speaker</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Adjournment is for a short period, Prorogation ends session</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Adjournment ends the House</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Adjournment is for a short period, Prorogation ends session</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Both Houses can initiate impeachment independently.</t>
+          <t>Adjournment is temporary; prorogation ends a session.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which article provides for the privileges of Parliament members?</t>
+          <t>In which year was the Anti-Defection Law added to the Constitution?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Article 108</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>This article grants MPs certain privileges and immunities.</t>
+          <t>It was added through the 52nd Amendment in 1985.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which session of Parliament is usually held from February to May?</t>
+          <t>Which of the following motions needs the support of at least 50 members to be admitted in Lok Sabha?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Monsoon Session</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Winter Session</t>
+          <t>No-confidence motion</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Budget Session</t>
+          <t>Censure motion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Special Session</t>
+          <t>Privilege motion</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Budget Session</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>It usually begins in February and includes the budget presentation.</t>
+          <t>It needs support of 50 members for admission.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>In which schedule is the anti-defection law mentioned?</t>
+          <t>Which House has more power in the case of a Money Bill?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8th Schedule</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>9th Schedule</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Both equal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>11th Schedule</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>The 10th Schedule was added by the 52nd Amendment for anti-defection.</t>
+          <t>Rajya Sabha can only make recommendations on Money Bills.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What is the term of nominated members of Rajya Sabha?</t>
+          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2 years</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Like elected members, nominated members also serve for 6 years.</t>
+          <t>He presides over joint sittings under Article 108.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The motion to remove the Vice President must be introduced in</t>
+          <t>What is the maximum gap between two sessions of Parliament?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>4 months</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>President’s Office</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Removal motion of Vice President must originate in Rajya Sabha.</t>
+          <t>There must not be more than a six-month gap between two sessions.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which of the following is not a parliamentary committee?</t>
+          <t>Which body examines the annual financial statement laid before Parliament?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Committee on Petitions</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Cabinet Committees are executive, not parliamentary.</t>
+          <t>The Public Accounts Committee examines the audit reports and financial accounts.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A bill becomes a law only after it is signed by</t>
+          <t>The first Lok Sabha was constituted in</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>President’s assent is essential for a bill to become a law.</t>
+          <t>The first Lok Sabha was formed in 1952 after the first general election.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What is the maximum time Rajya Sabha can hold a Money Bill?</t>
+          <t>What is the maximum number of members in Rajya Sabha from a single state?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7 days</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>21 days</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Rajya Sabha must return a Money Bill within 14 days; else it is deemed passed.</t>
+          <t>Uttar Pradesh sends the highest number (31) to Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What happens if there is a vacancy in the office of Speaker and Deputy Speaker of Lok Sabha?</t>
+          <t>What is the quorum of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>President presides over</t>
+          <t>15 members</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Prime Minister presides over</t>
+          <t>1/6th of total</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Member appointed by President presides</t>
+          <t>1/10th of total</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Any member appointed by the House presides</t>
+          <t>50 members</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Any member appointed by the House presides</t>
+          <t>1/10th of total</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>The House appoints a member to preside in absence of Speaker/Deputy Speaker.</t>
+          <t>Minimum 1/10th of the total strength is required to conduct business.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which of the following statements is true regarding the dissolution of Rajya Sabha?</t>
+          <t>Who can disqualify a Member of Parliament on grounds of defection?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>It is dissolved every 5 years</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>It is dissolved by the President</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>It is dissolved by the Prime Minister</t>
+          <t>Speaker or Chairman</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>It cannot be dissolved</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>It cannot be dissolved</t>
+          <t>Speaker or Chairman</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent house and is not subject to dissolution.</t>
+          <t>They decide disqualification under the 10th Schedule.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Parliament can legislate on a subject in the State List if</t>
+          <t>Which Article mentions the composition of the Rajya Sabha?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rajya Sabha passes a resolution</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>There is national emergency</t>
+          <t>Article 81</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>States request it</t>
+          <t>Article 82</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 83</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>All these are valid conditions under which Parliament can legislate on State subjects.</t>
+          <t>Article 80 of the Constitution deals with the composition of Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which is not required to pass a Constitutional Amendment Bill?</t>
+          <t>The first Speaker of Lok Sabha was</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Simple Majority</t>
+          <t>G V Mavalankar</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Special Majority</t>
+          <t>M A Ayyangar</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ratification by States</t>
+          <t>S Radhakrishnan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>President's assent</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Simple Majority</t>
+          <t>G V Mavalankar</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Most Constitutional Amendments require special majority, not simple majority.</t>
+          <t>He was the first Speaker of Lok Sabha after 1952 elections.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which of the following motions can lead to the fall of the Council of Ministers?</t>
+          <t>How many members can be nominated to the Rajya Sabha by the President?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Calling Attention Motion</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Adjournment Motion</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Censure Motion</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>No-confidence Motion</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No-confidence Motion</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>It expresses loss of confidence in the government.</t>
+          <t>The President can nominate 12 members to Rajya Sabha from fields like art, science, etc.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What is the minimum age to become a member of Rajya Sabha?</t>
+          <t>In case of deadlock between two Houses on a bill, who summons the joint sitting?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>25 years</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>30 years</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>35 years</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>21 years</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>30 years</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>A candidate must be at least 30 years old to be elected to Rajya Sabha.</t>
+          <t>President summons a joint session to resolve the deadlock.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which Article authorizes Parliament to make laws on State List during national emergency?</t>
+          <t>Under which article can Parliament punish a person for breach of privilege?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Article 107</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Article 118</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>During National Emergency, Parliament can legislate on State subjects under Article 250.</t>
+          <t>It includes the powers and privileges of Parliament members.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which of the following is true about Zero Hour?</t>
+          <t>Under normal circumstances, how many sessions of Parliament are held in a year?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>It is mentioned in Constitution</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>It begins at 12 noon</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>It is a procedural motion</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>It is started by Rajya Sabha</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>It begins at 12 noon</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Zero Hour starts at 12 PM and is an Indian innovation (not in Constitution).</t>
+          <t>Budget, Monsoon, and Winter Sessions are held annually.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The power to summon or prorogue Parliament rests with</t>
+          <t>How many members can the President nominate to Lok Sabha from Anglo-Indian community (until removed)?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>President summons and prorogues the Parliament on advice of Council of Ministers.</t>
+          <t>Till the 104th Amendment (2020), President could nominate 2 Anglo-Indians.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>How many members of Anglo-Indian community could be nominated to Lok Sabha (before 104th Amendment)?</t>
+          <t>Which motion is used to express disapproval of a specific policy of the government?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No-confidence motion</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Censure motion</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cut motion</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Censure motion</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Earlier, President could nominate 2 Anglo-Indians (now discontinued after 104th Amendment).</t>
+          <t>It expresses strong disapproval of a specific policy.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>In the event of a conflict between two Houses on an ordinary bill, the mechanism used is</t>
+          <t>Which article mentions the composition of Parliament?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Money Bill clause</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>President’s Order</t>
+          <t>Article 81</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Constitutional Amendment</t>
+          <t>Article 82</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Joint sitting is used to resolve deadlock on ordinary bills.</t>
+          <t>Article 79 states that Parliament consists of President, Lok Sabha, and Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The first Speaker of Lok Sabha was</t>
+          <t>Which of the following is NOT a function of Parliament?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>G V Mavalankar</t>
+          <t>Law-making</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>M A Ayyangar</t>
+          <t>Amending Constitution</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S Radhakrishnan</t>
+          <t>Controlling Executive</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Electing President</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>G V Mavalankar</t>
+          <t>Electing President</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>He was the first Speaker of Lok Sabha after 1952 elections.</t>
+          <t>President is elected by an electoral college, not Parliament alone.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
+          <t>Who can introduce a bill for Constitutional Amendment?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>Only Ministers</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Only Lok Sabha MP</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Any member of Parliament</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Vice President</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Lok Sabha Speaker</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Prime Minister</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>The Speaker of the Lok Sabha presides over joint sittings.</t>
+          <t>Both Ministers and private members can introduce Constitutional Amendments.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What is the term of a Rajya Sabha member?</t>
+          <t>Which article empowers the Parliament to make laws on State List under certain circumstances?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Article 263</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>7 years</t>
+          <t>Article 312</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Rajya Sabha members have a term of 6 years, with one-third retiring every two years.</t>
+          <t>Under Article 249, Rajya Sabha can pass a resolution allowing Parliament to legislate on State List.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which schedule of the Constitution contains the Anti-Defection Law?</t>
+          <t>Who is the custodian of the Lok Sabha?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8th</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>The Tenth Schedule deals with provisions regarding disqualification on the grounds of defection.</t>
+          <t>The Speaker is the guardian and controller of Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>What is the maximum strength of the Lok Sabha as per the Constitution?</t>
+          <t>The first hour of every parliamentary sitting is reserved for:</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>Debate</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>Question Hour</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>Private member bill</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>Question Hour</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>As per Article 81, the maximum strength is 552 members.</t>
+          <t>It is devoted to questions and answers.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which of the following is not a part of the Indian Parliament?</t>
+          <t>What is the maximum time limit within which Parliament must approve a Money Bill after it is introduced?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
-        </is>
-      </c>
+          <t>75 days</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>The Supreme Court is part of the Judiciary, not the Parliament.</t>
+          <t>Money Bill must be passed within 14 days by both Houses.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which of the following is not a function of Parliament?</t>
+          <t>Which of the following is NOT a type of bill in Indian Parliament?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>Appropriation Bill</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Executive appointments</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Amending Constitution</t>
+          <t>Judicial Bill</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Judicial Bill</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Judicial review is the function of courts, not Parliament.</t>
+          <t>There’s no such category; only legislative, money, financial bills exist.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Rajya Sabha can delay an ordinary bill by maximum of</t>
+          <t>The maximum gap between two sessions of Parliament cannot be more than</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4 months</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>6 months</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>3 months</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>1 month</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2538,2601 +2542,2597 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Rajya Sabha can delay an ordinary bill for maximum 6 months.</t>
+          <t>According to the Constitution, there must not be a gap of more than 6 months.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which authority decides the disqualification of MPs under anti-defection?</t>
+          <t>Who can introduce a Private Member Bill?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Only opposition MPs</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Any non-minister MP</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Speaker/Chairman</t>
+          <t>Only ruling party MP</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Only nominated MPs</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Speaker/Chairman</t>
+          <t>Any non-minister MP</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>The Presiding Officer decides under 10th Schedule.</t>
+          <t>Private Member Bills are introduced by MPs who are not Ministers.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What is the difference between adjournment and prorogation?</t>
+          <t>How many members of Anglo-Indian community could be nominated to Lok Sabha (before 104th Amendment)?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>No difference</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Adjournment by President, Prorogation by Speaker</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Adjournment is for a short period, Prorogation ends session</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Adjournment ends the House</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Adjournment is for a short period, Prorogation ends session</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Adjournment is temporary; prorogation ends a session.</t>
+          <t>Earlier, President could nominate 2 Anglo-Indians (now discontinued after 104th Amendment).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which body examines the annual financial statement laid before Parliament?</t>
+          <t>Which of the following statements is true regarding the dissolution of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>It is dissolved every 5 years</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>It is dissolved by the President</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>It is dissolved by the Prime Minister</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>It cannot be dissolved</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>It cannot be dissolved</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>The Public Accounts Committee examines the audit reports and financial accounts.</t>
+          <t>Rajya Sabha is a permanent house and is not subject to dissolution.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Who acts as the pro tem Speaker of Lok Sabha?</t>
+          <t>Which House is considered the Council of States?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Longest-serving MP</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Senior-most member</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Vice President</t>
-        </is>
-      </c>
+          <t>Vidhan Sabha</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Senior-most member</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>The senior-most member is appointed to conduct the first meeting until Speaker is elected.</t>
+          <t>Rajya Sabha represents the states and is called the Council of States.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
+          <t>Which of the following is a permanent House?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Vice President</t>
-        </is>
-      </c>
+          <t>Legislative Assembly</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>The Vice President of India is the ex-officio Chairman of Rajya Sabha.</t>
+          <t>Rajya Sabha is not subject to dissolution; one-third members retire every 2 years.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which of the following is not a function of Parliament?</t>
+          <t>Which of the following statements is true regarding Zero Hour?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>It is mentioned in Constitution</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Amending the Constitution</t>
+          <t>It starts at 11 AM</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Electing the President</t>
+          <t>It starts after lunch</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Enforcing laws</t>
+          <t>It is a parliamentary convention</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Enforcing laws</t>
+          <t>It is a parliamentary convention</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Enforcing laws is the function of the executive.</t>
+          <t>Zero Hour is not in the rulebook, it's a practice started in 1962.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Can the Rajya Sabha be dissolved?</t>
+          <t>In case of a deadlock between the two Houses, the President can summon a joint sitting under which article?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Yes, after 6 years</t>
+          <t>Article 108</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Yes, by the President</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 111</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Only in emergency</t>
+          <t>Article 112</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 108</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
+          <t>Joint sitting can be called to resolve deadlock between Houses.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Who decides whether a bill is a Money Bill or not?</t>
+          <t>What is the maximum gap allowed between two parliamentary sessions?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>4 months</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>5 months</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>As per Article 110, the Speaker's decision is final.</t>
+          <t>Parliament must meet at least once every six months.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which House is considered the Council of States?</t>
+          <t>Which motion is used to reduce the amount of a demand for grant?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Cut Motion</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>No-Confidence Motion</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vidhan Sabha</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>Censure Motion</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Privilege Motion</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Cut Motion</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Rajya Sabha represents the states and is called the Council of States.</t>
+          <t>Cut motions are used to oppose specific provisions in the budget.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The power to summon or prorogue the Parliament rests with?</t>
+          <t>The Speaker of Lok Sabha is elected by</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Lok Sabha members</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Lok Sabha members</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>The President summons and prorogues Parliament sessions.</t>
+          <t>Speaker is elected by members of Lok Sabha from among themselves.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The quorum for a meeting of either House of Parliament is?</t>
+          <t>A bill becomes a law only after it is signed by</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1/5th</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1/4th</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1/6th</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1/10th</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1/10th</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>The minimum number of members required to hold a meeting is 1/10th of the total strength.</t>
+          <t>President’s assent is essential for a bill to become a law.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Money Bills can be introduced only in which House?</t>
+          <t>What is the minimum age to become a member of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>25 years</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Either House</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>35 years</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>21 years</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Only Lok Sabha can introduce a Money Bill as per Article 110.</t>
+          <t>A candidate must be at least 30 years old to be elected to Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which Article mentions the composition of the Rajya Sabha?</t>
+          <t>What is the tenure of the members of the Rajya Sabha?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Article 81</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Article 82</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Article 83</t>
+          <t>Till dissolved</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Article 80 of the Constitution deals with the composition of Rajya Sabha.</t>
+          <t>One-third members retire every 2 years.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The first sitting of the Constituent Assembly took place in which year?</t>
+          <t>The motion to remove the Vice President must be introduced in</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>President’s Office</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>The Constituent Assembly first met on 9 December 1946.</t>
+          <t>Removal motion of Vice President must originate in Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which Article empowers the Parliament to make laws on State List during emergency?</t>
+          <t>Which schedule of the Constitution deals with allocation of seats in Rajya Sabha?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>First</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Fourth</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Article 248</t>
+          <t>Sixth</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Fourth</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Parliament can legislate on state subjects during National Emergency under Article 250.</t>
+          <t>The Fourth Schedule allocates seats in Rajya Sabha to states and UTs.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What is the tenure of the Speaker of Lok Sabha?</t>
+          <t>Which House of Parliament can initiate impeachment of the President?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Lok Sabha only</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Rajya Sabha only</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Till next election</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Till he/she resigns or removed</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Till he/she resigns or removed</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Speaker holds office until removed or resignation, even after dissolution.</t>
+          <t>Both Houses can initiate impeachment independently.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which Committee examines the report of the Comptroller and Auditor General (CAG)?</t>
+          <t>The Rajya Sabha can delay an ordinary bill by maximum of</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Privileges Committee</t>
+          <t>1 month</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Business Advisory Committee</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>PAC examines CAG reports and ensures public money is spent properly.</t>
+          <t>Rajya Sabha can delay an ordinary bill for maximum 6 months.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which constitutional amendment lowered the voting age from 21 to 18?</t>
+          <t>In the event of a conflict between two Houses on an ordinary bill, the mechanism used is</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>42nd</t>
+          <t>Money Bill clause</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>44th</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>61st</t>
+          <t>President’s Order</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>52nd</t>
+          <t>Constitutional Amendment</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>61st</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>The 61st Amendment Act, 1989, reduced the voting age.</t>
+          <t>Joint sitting is used to resolve deadlock on ordinary bills.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>In which year was the Parliament House of India inaugurated?</t>
+          <t>Who decides whether a Bill is a Money Bill or not?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>The current Parliament House was inaugurated in 1927 by Lord Irwin.</t>
+          <t>Speaker’s decision is final under Article 110.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Who can introduce an ordinary bill in Parliament?</t>
+          <t>How many types of major parliamentary committees exist in India?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Only Minister</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Only MP from ruling party</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Only Lok Sabha MP</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Ordinary Bills can be introduced by any MP.</t>
+          <t>Standing and Ad-hoc are the two main types.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>In case of deadlock between two Houses on a bill, who summons the joint sitting?</t>
+          <t>Can Rajya Sabha be dissolved?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Yes, every 6 years</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Yes, every 5 years</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Yes, at the discretion of President</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>President summons a joint session to resolve the deadlock.</t>
+          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The maximum number of nominated members in Rajya Sabha is?</t>
+          <t>Which committee is called the “watchdog of public purse”?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Committee on Subordinate Legislation</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Committee on Public Undertakings</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>The President can nominate 12 members with special knowledge in fields like art, literature, etc.</t>
+          <t>It ensures accountability in public spending.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which of the following is NOT true about Rajya Sabha?</t>
+          <t>What is the quorum to conduct a sitting of either House of Parliament?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>It is a permanent House</t>
+          <t>1/5th of total membership</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>It has equal powers with Lok Sabha on Money Bills</t>
+          <t>1/10th of total membership</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>It represents states</t>
+          <t>1/3rd of total membership</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>It has 250 members</t>
+          <t>Half the total strength</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>It has equal powers with Lok Sabha on Money Bills</t>
+          <t>1/10th of total membership</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Rajya Sabha has limited role in Money Bills.</t>
+          <t>Quorum is 1/10th of total strength of the House.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Who is the custodian of the Lok Sabha?</t>
+          <t>Which of the following motions can lead to the fall of the Council of Ministers?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Calling Attention Motion</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Adjournment Motion</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Censure Motion</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>No-confidence Motion</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>No-confidence Motion</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>The Speaker is the guardian and controller of Lok Sabha.</t>
+          <t>It expresses loss of confidence in the government.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a function of the Estimates Committee?</t>
+          <t>The concept of Parliamentary Privileges in India is taken from which country?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Suggesting economic improvements</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Examining estimates in Budget</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Examining CAG reports</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ensuring efficient allocation</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Examining CAG reports</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>That's the job of Public Accounts Committee, not Estimates Committee.</t>
+          <t>India borrowed Parliamentary Privileges from the British system.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>What happens if there is a deadlock on a Constitutional Amendment Bill?</t>
+          <t>Who presides over the joint sitting of Parliament?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Joint Sitting is held</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>President decides</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lok Sabha prevails</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bill fails</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bill fails</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>There is no provision for joint sitting on Constitutional Amendments.</t>
+          <t>In joint sittings, the Speaker of Lok Sabha presides.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which Article deals with the procedure in financial matters like Budget?</t>
+          <t>Which House of Parliament is considered more powerful in terms of money matters?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Article 109</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Article 112</t>
+          <t>Both equal</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>It governs financial bills other than money bills.</t>
+          <t>Money Bills can only be introduced and passed in the Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>How many members can the President nominate to Lok Sabha from Anglo-Indian community (until removed)?</t>
+          <t>Money Bills can be introduced only in which House?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Either House</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Till the 104th Amendment (2020), President could nominate 2 Anglo-Indians.</t>
+          <t>Only Lok Sabha can introduce a Money Bill as per Article 110.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which of the following motions needs the support of at least 50 members to be admitted in Lok Sabha?</t>
+          <t>Which of the following motions is NOT related to financial matters?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>Cut Motion</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>No-confidence motion</t>
+          <t>Adjournment Motion</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Censure motion</t>
+          <t>Appropriation Bill</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Privilege motion</t>
+          <t>Finance Bill</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>Adjournment Motion</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>It needs support of 50 members for admission.</t>
+          <t>It is used to draw attention to urgent matters, not financial matters.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>How many types of major parliamentary committees exist in India?</t>
+          <t>Which authority decides the disqualification of MPs under anti-defection?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Speaker/Chairman</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Speaker/Chairman</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Standing and Ad-hoc are the two main types.</t>
+          <t>The Presiding Officer decides under 10th Schedule.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which of the following statements is correct regarding Money Bill?</t>
+          <t>What is the maximum tenure of Lok Sabha?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>It needs approval of Rajya Sabha</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Rajya Sabha can reject it</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rajya Sabha can suggest amendments</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rajya Sabha can amend it</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rajya Sabha can suggest amendments</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Rajya Sabha can only suggest, not amend or reject it.</t>
+          <t>Lok Sabha has a normal term of 5 years unless dissolved earlier.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Who can disqualify a Member of Parliament on grounds of defection?</t>
+          <t>The Parliament can legislate on a subject in the State List if</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Rajya Sabha passes a resolution</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>There is national emergency</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Speaker or Chairman</t>
+          <t>States request it</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Speaker or Chairman</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>They decide disqualification under the 10th Schedule.</t>
+          <t>All these are valid conditions under which Parliament can legislate on State subjects.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which Article allows the Parliament to make laws on a matter in the State List under national interest?</t>
+          <t>Can the Rajya Sabha be dissolved?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>Yes, after 6 years</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Yes, by the President</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>Only in emergency</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Rajya Sabha can authorize Parliament to legislate on State List in national interest.</t>
+          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which provision ensures that Parliament remains sovereign in making laws?</t>
+          <t>Which of the following bills cannot be introduced in Rajya Sabha?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Doctrine of pith and substance</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Basic structure</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>Constitution Amendment Bill</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Financial Bill (Type II)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Doctrine of pith and substance</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>It gives Parliament flexibility in legislative matters.</t>
+          <t>Only Lok Sabha can introduce a Money Bill.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Who can introduce a bill for Constitutional Amendment?</t>
+          <t>Which article empowers Parliament to create new states?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Only Ministers</t>
+          <t>Article 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Only Lok Sabha MP</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Article 1</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Both Ministers and private members can introduce Constitutional Amendments.</t>
+          <t>Parliament can form new states or alter existing ones.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>What is the quorum of Rajya Sabha?</t>
+          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>15 members</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1/6th of total</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1/10th of total</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>50 members</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1/10th of total</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Minimum 1/10th of the total strength is required to conduct business.</t>
+          <t>As per Article 64, Vice President is ex-officio Chairman of Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>In which year was the Anti-Defection Law added to the Constitution?</t>
+          <t>Which of the following is true about Zero Hour?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>It is mentioned in Constitution</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>It begins at 12 noon</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>It is a procedural motion</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>It is started by Rajya Sabha</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>It begins at 12 noon</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>It was added through the 52nd Amendment in 1985.</t>
+          <t>Zero Hour starts at 12 PM and is an Indian innovation (not in Constitution).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>What is the maximum gap allowed between two parliamentary sessions?</t>
+          <t>Which House of Parliament has special powers regarding creation of All-India Services?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>4 months</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>5 months</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>6 months</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Parliament must meet at least once every six months.</t>
+          <t>Rajya Sabha can pass a resolution to create All-India Services.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which Article empowers Parliament to create new states?</t>
+          <t>Which article provides for the privileges of Parliament members?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Article 2</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>Article 108</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Article 4</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Article 5</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>It gives Parliament power to create or alter state boundaries.</t>
+          <t>This article grants MPs certain privileges and immunities.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>How many readings does a bill go through in the Parliament?</t>
+          <t>The power to summon or prorogue Parliament rests with</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Each House of Parliament conducts 3 readings: introduction, consideration, and passing.</t>
+          <t>President summons and prorogues the Parliament on advice of Council of Ministers.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a type of bill in Indian Parliament?</t>
+          <t>Which Article deals with the procedure in financial matters like Budget?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Appropriation Bill</t>
+          <t>Article 109</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Article 112</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Judicial Bill</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Judicial Bill</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>There’s no such category; only legislative, money, financial bills exist.</t>
+          <t>It governs financial bills other than money bills.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which committee is called the “watchdog of public purse”?</t>
+          <t>Which constitutional amendment lowered the voting age from 21 to 18?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>42nd</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>44th</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Committee on Subordinate Legislation</t>
+          <t>61st</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Committee on Public Undertakings</t>
+          <t>52nd</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>61st</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>It ensures accountability in public spending.</t>
+          <t>The 61st Amendment Act, 1989, reduced the voting age.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>In which case did the Supreme Court rule that Parliament cannot alter the Basic Structure?</t>
+          <t>What is the maximum time Rajya Sabha can hold a Money Bill?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Minerva Mills v. Union of India</t>
+          <t>7 days</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Golak Nath v. State of Punjab</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati v. State of Kerala</t>
+          <t>21 days</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SR Bommai v. Union of India</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati v. State of Kerala</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>This judgment introduced the Basic Structure doctrine.</t>
+          <t>Rajya Sabha must return a Money Bill within 14 days; else it is deemed passed.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which article empowers the Parliament to make laws on State List under certain circumstances?</t>
+          <t>Which body recommends disqualification of members on grounds of defection?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>Speaker/Chairman</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Article 263</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Article 312</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>Speaker/Chairman</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Under Article 249, Rajya Sabha can pass a resolution allowing Parliament to legislate on State List.</t>
+          <t>Presiding officer decides on disqualification under anti-defection law.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>How many times can the President summon Parliament in a year at minimum?</t>
+          <t>In case of a deadlock between the two Houses, how is the issue resolved?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>President’s Rule</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Prime Minister’s veto</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>There must be at least two sessions in a year as per Article 85.</t>
+          <t>A joint sitting of Parliament is called under Article 108.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which House of Parliament is considered more powerful in terms of money matters?</t>
+          <t>Which of the following statements is incorrect regarding the Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>He/she can vote in first instance</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>He/she is elected from among Lok Sabha members</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Both equal</t>
+          <t>He/she can disqualify a member under anti-defection law</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>He/she is subordinate to the President</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>He/she is subordinate to the President</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Money Bills can only be introduced and passed in the Lok Sabha.</t>
+          <t>Speaker is not subordinate to anyone; he is the constitutional authority.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What is the quorum to constitute a meeting of the Lok Sabha?</t>
+          <t>How many houses does the Indian Parliament consist of?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1/2 of total members</t>
+          <t>One</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1/10 of total members</t>
+          <t>Two</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1/5 of total members</t>
+          <t>Three</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1/4 of total members</t>
+          <t>Four</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1/10 of total members</t>
+          <t>Two</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Quorum is the minimum number of members required to hold a sitting.</t>
+          <t>The Indian Parliament has two houses – Lok Sabha and Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which Schedule of the Constitution contains provisions relating to disqualification on the grounds of defection?</t>
+          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>9th Schedule</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>12th Schedule</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>10th Schedule deals with anti-defection law as added by the 52nd Amendment.</t>
+          <t>The Vice President of India is the ex-officio Chairman of Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Which of the following statements is true regarding Zero Hour?</t>
+          <t>Who decides whether a bill is a Money Bill or not?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>It is mentioned in Constitution</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>It starts at 11 AM</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>It starts after lunch</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>It is a parliamentary convention</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>It is a parliamentary convention</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Zero Hour is not in the rulebook, it's a practice started in 1962.</t>
+          <t>As per Article 110, the Speaker's decision is final.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Which Article provides for the privileges of Parliament?</t>
+          <t>What happens if there is a deadlock on a Constitutional Amendment Bill?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Article 104</t>
+          <t>Joint Sitting is held</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>President decides</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Article 106</t>
+          <t>Lok Sabha prevails</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Bill fails</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>Bill fails</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>It provides for the powers, privileges and immunities of Parliament and its members.</t>
+          <t>There is no provision for joint sitting on Constitutional Amendments.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Which motion is used to express disapproval of a specific policy of the government?</t>
+          <t>Which Article empowers the Parliament to make laws on State List during emergency?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>No-confidence motion</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Censure motion</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cut motion</t>
+          <t>Article 248</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Censure motion</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>It expresses strong disapproval of a specific policy.</t>
+          <t>Parliament can legislate on state subjects during National Emergency under Article 250.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Who can introduce a Private Member Bill?</t>
+          <t>Which of the following is not a function of Parliament?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Only opposition MPs</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Any non-minister MP</t>
+          <t>Executive appointments</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Only ruling party MP</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Only nominated MPs</t>
+          <t>Amending Constitution</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Any non-minister MP</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Private Member Bills are introduced by MPs who are not Ministers.</t>
+          <t>Judicial review is the function of courts, not Parliament.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>What is the maximum number of members in Rajya Sabha from a single state?</t>
+          <t>The maximum strength of the Lok Sabha is</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>545</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>552</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>560</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Uttar Pradesh sends the highest number (31) to Rajya Sabha.</t>
+          <t>According to Article 81, the Lok Sabha can have up to 552 members.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Who decides whether a Bill is a Money Bill or not?</t>
+          <t>What is the current maximum strength of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>245</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>238</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Speaker’s decision is final under Article 110.</t>
+          <t>Rajya Sabha can have up to 250 members, out of which 12 are nominated.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Which of the following motions is NOT related to financial matters?</t>
+          <t>What is the term of nominated members of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cut Motion</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Adjournment Motion</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Appropriation Bill</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Finance Bill</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Adjournment Motion</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>It is used to draw attention to urgent matters, not financial matters.</t>
+          <t>Like elected members, nominated members also serve for 6 years.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>What is the tenure of the members of the Rajya Sabha?</t>
+          <t>Which article of the Constitution deals with the composition of the Parliament?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Article 81</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Till dissolved</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>One-third members retire every 2 years.</t>
+          <t>Article 79 defines the structure of the Indian Parliament.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Which House of Parliament is not subject to dissolution?</t>
+          <t>How many times can the President summon Parliament in a year at minimum?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent House, not subject to dissolution.</t>
+          <t>There must be at least two sessions in a year as per Article 85.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>The term ‘Zero Hour’ refers to</t>
+          <t>The quorum for a meeting of either House of Parliament is?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>First hour after lunch</t>
+          <t>1/5th</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Time before Question Hour</t>
+          <t>1/4th</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Time immediately after Question Hour</t>
+          <t>1/6th</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Time after adjournment</t>
+          <t>1/10th</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Time immediately after Question Hour</t>
+          <t>1/10th</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Zero Hour is an Indian innovation, used to raise urgent matters.</t>
+          <t>The minimum number of members required to hold a meeting is 1/10th of the total strength.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>The concept of Parliamentary Privileges in India is taken from which country?</t>
+          <t>Which Schedule of the Constitution contains provisions relating to disqualification on the grounds of defection?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>9th Schedule</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>12th Schedule</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>India borrowed Parliamentary Privileges from the British system.</t>
+          <t>10th Schedule deals with anti-defection law as added by the 52nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Which of the following bills cannot be introduced in Rajya Sabha?</t>
+          <t>Money Bill can be introduced only in</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Constitution Amendment Bill</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Financial Bill (Type II)</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Only Lok Sabha can introduce a Money Bill.</t>
+          <t>Money Bills can be introduced only in Lok Sabha, as per Article 110.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which of the following statements is incorrect regarding the Speaker of Lok Sabha?</t>
+          <t>Which House of Parliament is not subject to dissolution?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>He/she can vote in first instance</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>He/she is elected from among Lok Sabha members</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>He/she can disqualify a member under anti-defection law</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>He/she is subordinate to the President</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>He/she is subordinate to the President</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Speaker is not subordinate to anyone; he is the constitutional authority.</t>
+          <t>Rajya Sabha is a permanent House, not subject to dissolution.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>In case of a deadlock between the two Houses, how is the issue resolved?</t>
+          <t>How many readings does a bill go through in the Parliament?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>President’s Rule</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Prime Minister’s veto</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>A joint sitting of Parliament is called under Article 108.</t>
+          <t>Each House of Parliament conducts 3 readings: introduction, consideration, and passing.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>What is the maximum time limit within which Parliament must approve a Money Bill after it is introduced?</t>
+          <t>Which Article empowers Parliament to create new states?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>Article 2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>75 days</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
+          <t>Article 4</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Article 5</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Money Bill must be passed within 14 days by both Houses.</t>
+          <t>It gives Parliament power to create or alter state boundaries.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Which article mentions the composition of Parliament?</t>
+          <t>Which Committee examines the report of the Comptroller and Auditor General (CAG)?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Article 81</t>
+          <t>Privileges Committee</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Article 82</t>
+          <t>Business Advisory Committee</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Article 79 states that Parliament consists of President, Lok Sabha, and Rajya Sabha.</t>
+          <t>PAC examines CAG reports and ensures public money is spent properly.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Which motion is used to reduce the amount of a demand for grant?</t>
+          <t>In which case did the Supreme Court rule that Parliament cannot alter the Basic Structure?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cut Motion</t>
+          <t>Minerva Mills v. Union of India</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>No-Confidence Motion</t>
+          <t>Golak Nath v. State of Punjab</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Censure Motion</t>
+          <t>Keshavananda Bharati v. State of Kerala</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Privilege Motion</t>
+          <t>SR Bommai v. Union of India</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cut Motion</t>
+          <t>Keshavananda Bharati v. State of Kerala</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Cut motions are used to oppose specific provisions in the budget.</t>
+          <t>This judgment introduced the Basic Structure doctrine.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a part of Parliament?</t>
+          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5142,227 +5142,227 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>He is part of Judiciary, not Legislature.</t>
+          <t>The Speaker of the Lok Sabha presides over joint sittings.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Which body recommends disqualification of members on grounds of defection?</t>
+          <t>What is the term of a Rajya Sabha member?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Speaker/Chairman</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>7 years</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Speaker/Chairman</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Presiding officer decides on disqualification under anti-defection law.</t>
+          <t>Rajya Sabha members have a term of 6 years, with one-third retiring every two years.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Which of the following statements is true about Private Member’s Bill?</t>
+          <t>Which session of Parliament is usually held from February to May?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Introduced only by ministers</t>
+          <t>Monsoon Session</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Introduced only in Lok Sabha</t>
+          <t>Winter Session</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Introduced by any MP not a minister</t>
+          <t>Budget Session</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Requires President’s assent first</t>
+          <t>Special Session</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Introduced by any MP not a minister</t>
+          <t>Budget Session</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Private Members are MPs who are not part of the executive.</t>
+          <t>It usually begins in February and includes the budget presentation.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
+          <t>Which of the following is not a parliamentary committee?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Committee on Petitions</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>He presides over joint sittings under Article 108.</t>
+          <t>Cabinet Committees are executive, not parliamentary.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>The first hour of every parliamentary sitting is reserved for:</t>
+          <t>Which Article provides for the privileges of Parliament?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>Article 104</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Debate</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Question Hour</t>
+          <t>Article 106</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Private member bill</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Question Hour</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>It is devoted to questions and answers.</t>
+          <t>It provides for the powers, privileges and immunities of Parliament and its members.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Under which article can Parliament punish a person for breach of privilege?</t>
+          <t>Which Article allows the Parliament to make laws on a matter in the State List under national interest?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Article 107</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Article 118</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>It includes the powers and privileges of Parliament members.</t>
+          <t>Rajya Sabha can authorize Parliament to legislate on State List in national interest.</t>
         </is>
       </c>
     </row>
@@ -5372,77 +5372,77 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>What is the maximum gap between two sessions of Parliament?</t>
+          <t>The maximum number of nominated members in Rajya Sabha is?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>4 months</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>There must not be more than a six-month gap between two sessions.</t>
+          <t>The President can nominate 12 members with special knowledge in fields like art, literature, etc.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which article empowers Parliament to create new states?</t>
+          <t>Which article of the Constitution defines a Money Bill?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Article 2</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>Article 112</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Article 1</t>
+          <t>Article 113</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Article 5</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Parliament can form new states or alter existing ones.</t>
+          <t>This article gives the definition of a Money Bill.</t>
         </is>
       </c>
     </row>

--- a/Data/IPParliament.xlsx
+++ b/Data/IPParliament.xlsx
@@ -472,1161 +472,1149 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Who decides whether a bill is a Money Bill or not?</t>
+          <t>Which of the following is NOT a type of bill in Indian Parliament?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>Appropriation Bill</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Judicial Bill</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Judicial Bill</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The Speaker’s decision on Money Bill is final under Article 110.</t>
+          <t>There’s no such category; only legislative, money, financial bills exist.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which provision ensures that Parliament remains sovereign in making laws?</t>
+          <t>What happens if there is a vacancy in the office of Speaker and Deputy Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Doctrine of pith and substance</t>
+          <t>President presides over</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Basic structure</t>
+          <t>Prime Minister presides over</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>Member appointed by President presides</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Any member appointed by the House presides</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Doctrine of pith and substance</t>
+          <t>Any member appointed by the House presides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>It gives Parliament flexibility in legislative matters.</t>
+          <t>The House appoints a member to preside in absence of Speaker/Deputy Speaker.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a part of Parliament?</t>
+          <t>Which of the following motions needs the support of at least 50 members to be admitted in Lok Sabha?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>No-confidence motion</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Censure motion</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Privilege motion</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>He is part of Judiciary, not Legislature.</t>
+          <t>It needs support of 50 members for admission.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which Article authorizes Parliament to make laws on State List during national emergency?</t>
+          <t>Which schedule of the Constitution contains the Anti-Defection Law?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>7th</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>8th</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>9th</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>During National Emergency, Parliament can legislate on State subjects under Article 250.</t>
+          <t>The Tenth Schedule deals with provisions regarding disqualification on the grounds of defection.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What is the tenure of the Speaker of Lok Sabha?</t>
+          <t>The term ‘Zero Hour’ refers to</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>First hour after lunch</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Time before Question Hour</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Till next election</t>
+          <t>Time immediately after Question Hour</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Till he/she resigns or removed</t>
+          <t>Time after adjournment</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Till he/she resigns or removed</t>
+          <t>Time immediately after Question Hour</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Speaker holds office until removed or resignation, even after dissolution.</t>
+          <t>Zero Hour is an Indian innovation, used to raise urgent matters.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What happens if there is a vacancy in the office of Speaker and Deputy Speaker of Lok Sabha?</t>
+          <t>What is the tenure of the members of the Rajya Sabha?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>President presides over</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Prime Minister presides over</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Member appointed by President presides</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Any member appointed by the House presides</t>
+          <t>Till dissolved</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Any member appointed by the House presides</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>The House appoints a member to preside in absence of Speaker/Deputy Speaker.</t>
+          <t>One-third members retire every 2 years.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a function of the Estimates Committee?</t>
+          <t>Which Article deals with the procedure in financial matters like Budget?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Suggesting economic improvements</t>
+          <t>Article 109</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Examining estimates in Budget</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Examining CAG reports</t>
+          <t>Article 112</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ensuring efficient allocation</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Examining CAG reports</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>That's the job of Public Accounts Committee, not Estimates Committee.</t>
+          <t>It governs financial bills other than money bills.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which of the following statements is true about Private Member’s Bill?</t>
+          <t>The first Speaker of Lok Sabha was</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Introduced only by ministers</t>
+          <t>G V Mavalankar</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Introduced only in Lok Sabha</t>
+          <t>M A Ayyangar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Introduced by any MP not a minister</t>
+          <t>S Radhakrishnan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Requires President’s assent first</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Introduced by any MP not a minister</t>
+          <t>G V Mavalankar</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Private Members are MPs who are not part of the executive.</t>
+          <t>He was the first Speaker of Lok Sabha after 1952 elections.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which schedule of the Constitution contains the Anti-Defection Law?</t>
+          <t>Which article mentions the composition of Parliament?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8th</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>Article 81</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>Article 82</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>The Tenth Schedule deals with provisions regarding disqualification on the grounds of defection.</t>
+          <t>Article 79 states that Parliament consists of President, Lok Sabha, and Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>In which year was the Parliament House of India inaugurated?</t>
+          <t>Which of the following is not a parliamentary committee?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>Committee on Petitions</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>The current Parliament House was inaugurated in 1927 by Lord Irwin.</t>
+          <t>Cabinet Committees are executive, not parliamentary.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Can a non-member of Parliament become a minister?</t>
+          <t>Which Article provides for the privileges of Parliament?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 104</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Yes, for 3 months</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>Article 106</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yes, for 1 year</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>He must get elected to either House within 6 months.</t>
+          <t>It provides for the powers, privileges and immunities of Parliament and its members.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which of the following statements is correct regarding Money Bill?</t>
+          <t>Under which article can Parliament punish a person for breach of privilege?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>It needs approval of Rajya Sabha</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rajya Sabha can reject it</t>
+          <t>Article 107</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rajya Sabha can suggest amendments</t>
+          <t>Article 118</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rajya Sabha can amend it</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rajya Sabha can suggest amendments</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Rajya Sabha can only suggest, not amend or reject it.</t>
+          <t>It includes the powers and privileges of Parliament members.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The power to summon or prorogue the Parliament rests with?</t>
+          <t>Which constitutional amendment lowered the voting age from 21 to 18?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>42nd</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>44th</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>61st</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>52nd</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>61st</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>The President summons and prorogues Parliament sessions.</t>
+          <t>The 61st Amendment Act, 1989, reduced the voting age.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which of the following is not a function of Parliament?</t>
+          <t>Which Article empowers Parliament to create new states?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>Article 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Amending the Constitution</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Electing the President</t>
+          <t>Article 4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Enforcing laws</t>
+          <t>Article 5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Enforcing laws</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Enforcing laws is the function of the executive.</t>
+          <t>It gives Parliament power to create or alter state boundaries.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>What is the maximum strength of the Lok Sabha as per the Constitution?</t>
+          <t>What is the maximum gap allowed between two parliamentary sessions?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>4 months</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>5 months</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>As per Article 81, the maximum strength is 552 members.</t>
+          <t>Parliament must meet at least once every six months.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Who acts as the pro tem Speaker of Lok Sabha?</t>
+          <t>What is the maximum number of members in Rajya Sabha from a single state?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Longest-serving MP</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Senior-most member</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Senior-most member</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>The senior-most member is appointed to conduct the first meeting until Speaker is elected.</t>
+          <t>Uttar Pradesh sends the highest number (31) to Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which of the following is NOT true about Rajya Sabha?</t>
+          <t>The first Lok Sabha was constituted in</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>It is a permanent House</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>It has equal powers with Lok Sabha on Money Bills</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>It represents states</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>It has 250 members</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>It has equal powers with Lok Sabha on Money Bills</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Rajya Sabha has limited role in Money Bills.</t>
+          <t>The first Lok Sabha was formed in 1952 after the first general election.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The first sitting of the Constituent Assembly took place in which year?</t>
+          <t>Which body examines the annual financial statement laid before Parliament?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>The Constituent Assembly first met on 9 December 1946.</t>
+          <t>The Public Accounts Committee examines the audit reports and financial accounts.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which is not required to pass a Constitutional Amendment Bill?</t>
+          <t>Which House is considered the Council of States?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Simple Majority</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Special Majority</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ratification by States</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>President's assent</t>
-        </is>
-      </c>
+          <t>Vidhan Sabha</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Simple Majority</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Most Constitutional Amendments require special majority, not simple majority.</t>
+          <t>Rajya Sabha represents the states and is called the Council of States.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>In which schedule is the anti-defection law mentioned?</t>
+          <t>Which schedule of the Constitution deals with allocation of seats in Rajya Sabha?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8th Schedule</t>
+          <t>First</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9th Schedule</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Fourth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>11th Schedule</t>
+          <t>Sixth</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Fourth</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>The 10th Schedule was added by the 52nd Amendment for anti-defection.</t>
+          <t>The Fourth Schedule allocates seats in Rajya Sabha to states and UTs.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The term ‘Zero Hour’ refers to</t>
+          <t>What is the term of nominated members of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>First hour after lunch</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Time before Question Hour</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Time immediately after Question Hour</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Time after adjournment</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Time immediately after Question Hour</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Zero Hour is an Indian innovation, used to raise urgent matters.</t>
+          <t>Like elected members, nominated members also serve for 6 years.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Who can introduce an ordinary bill in Parliament?</t>
+          <t>What is the quorum to conduct a sitting of either House of Parliament?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Only Minister</t>
+          <t>1/5th of total membership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Only MP from ruling party</t>
+          <t>1/10th of total membership</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>1/3rd of total membership</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Only Lok Sabha MP</t>
+          <t>Half the total strength</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>1/10th of total membership</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Ordinary Bills can be introduced by any MP.</t>
+          <t>Quorum is 1/10th of total strength of the House.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which of the following is not a part of the Indian Parliament?</t>
+          <t>Which of the following motions is NOT related to financial matters?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Cut Motion</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Adjournment Motion</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Appropriation Bill</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Finance Bill</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Adjournment Motion</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>The Supreme Court is part of the Judiciary, not the Parliament.</t>
+          <t>It is used to draw attention to urgent matters, not financial matters.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What is the quorum to constitute a meeting of the Lok Sabha?</t>
+          <t>Which authority decides the disqualification of MPs under anti-defection?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1/2 of total members</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1/10 of total members</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1/5 of total members</t>
+          <t>Speaker/Chairman</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1/4 of total members</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1/10 of total members</t>
+          <t>Speaker/Chairman</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Quorum is the minimum number of members required to hold a sitting.</t>
+          <t>The Presiding Officer decides under 10th Schedule.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What is the difference between adjournment and prorogation?</t>
+          <t>In which case did the Supreme Court rule that Parliament cannot alter the Basic Structure?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No difference</t>
+          <t>Minerva Mills v. Union of India</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Adjournment by President, Prorogation by Speaker</t>
+          <t>Golak Nath v. State of Punjab</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Adjournment is for a short period, Prorogation ends session</t>
+          <t>Keshavananda Bharati v. State of Kerala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Adjournment ends the House</t>
+          <t>SR Bommai v. Union of India</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Adjournment is for a short period, Prorogation ends session</t>
+          <t>Keshavananda Bharati v. State of Kerala</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Adjournment is temporary; prorogation ends a session.</t>
+          <t>This judgment introduced the Basic Structure doctrine.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>In which year was the Anti-Defection Law added to the Constitution?</t>
+          <t>Which Committee examines the report of the Comptroller and Auditor General (CAG)?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>Privileges Committee</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>Business Advisory Committee</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>It was added through the 52nd Amendment in 1985.</t>
+          <t>PAC examines CAG reports and ensures public money is spent properly.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which of the following motions needs the support of at least 50 members to be admitted in Lok Sabha?</t>
+          <t>Which of the following is a permanent House?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>No-confidence motion</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Censure motion</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Privilege motion</t>
-        </is>
-      </c>
+          <t>Legislative Assembly</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>It needs support of 50 members for admission.</t>
+          <t>Rajya Sabha is not subject to dissolution; one-third members retire every 2 years.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which House has more power in the case of a Money Bill?</t>
+          <t>What is the maximum time limit within which Parliament must approve a Money Bill after it is introduced?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Both equal</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+          <t>75 days</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Rajya Sabha can only make recommendations on Money Bills.</t>
+          <t>Money Bill must be passed within 14 days by both Houses.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
+          <t>In which year was the Anti-Defection Law added to the Constitution?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>He presides over joint sittings under Article 108.</t>
+          <t>It was added through the 52nd Amendment in 1985.</t>
         </is>
       </c>
     </row>
@@ -1672,171 +1660,171 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which body examines the annual financial statement laid before Parliament?</t>
+          <t>Who acts as the pro tem Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Longest-serving MP</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>Senior-most member</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>Senior-most member</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>The Public Accounts Committee examines the audit reports and financial accounts.</t>
+          <t>The senior-most member is appointed to conduct the first meeting until Speaker is elected.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The first Lok Sabha was constituted in</t>
+          <t>Which Article empowers the Parliament to make laws on State List during emergency?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Article 248</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>The first Lok Sabha was formed in 1952 after the first general election.</t>
+          <t>Parliament can legislate on state subjects during National Emergency under Article 250.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What is the maximum number of members in Rajya Sabha from a single state?</t>
+          <t>Which motion is used to reduce the amount of a demand for grant?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Cut Motion</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>No-Confidence Motion</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>Censure Motion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>Privilege Motion</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Cut Motion</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Uttar Pradesh sends the highest number (31) to Rajya Sabha.</t>
+          <t>Cut motions are used to oppose specific provisions in the budget.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What is the quorum of Rajya Sabha?</t>
+          <t>How many readings does a bill go through in the Parliament?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15 members</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1/6th of total</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1/10th of total</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>50 members</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1/10th of total</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Minimum 1/10th of the total strength is required to conduct business.</t>
+          <t>Each House of Parliament conducts 3 readings: introduction, consideration, and passing.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Who can disqualify a Member of Parliament on grounds of defection?</t>
+          <t>The Speaker of Lok Sabha is elected by</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1846,452 +1834,448 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Lok Sabha members</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Speaker or Chairman</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Speaker or Chairman</t>
+          <t>Lok Sabha members</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>They decide disqualification under the 10th Schedule.</t>
+          <t>Speaker is elected by members of Lok Sabha from among themselves.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which Article mentions the composition of the Rajya Sabha?</t>
+          <t>In case of deadlock between two Houses on a bill, who summons the joint sitting?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Article 81</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Article 82</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Article 83</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Article 80 of the Constitution deals with the composition of Rajya Sabha.</t>
+          <t>President summons a joint session to resolve the deadlock.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The first Speaker of Lok Sabha was</t>
+          <t>Which of the following is NOT a function of the Estimates Committee?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>G V Mavalankar</t>
+          <t>Suggesting economic improvements</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>M A Ayyangar</t>
+          <t>Examining estimates in Budget</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S Radhakrishnan</t>
+          <t>Examining CAG reports</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Ensuring efficient allocation</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>G V Mavalankar</t>
+          <t>Examining CAG reports</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>He was the first Speaker of Lok Sabha after 1952 elections.</t>
+          <t>That's the job of Public Accounts Committee, not Estimates Committee.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>How many members can be nominated to the Rajya Sabha by the President?</t>
+          <t>A bill becomes a law only after it is signed by</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>The President can nominate 12 members to Rajya Sabha from fields like art, science, etc.</t>
+          <t>President’s assent is essential for a bill to become a law.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>In case of deadlock between two Houses on a bill, who summons the joint sitting?</t>
+          <t>Which House of Parliament is not subject to dissolution?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Speaker</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>President summons a joint session to resolve the deadlock.</t>
+          <t>Rajya Sabha is a permanent House, not subject to dissolution.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Under which article can Parliament punish a person for breach of privilege?</t>
+          <t>Who can introduce a bill for Constitutional Amendment?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>Only Ministers</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Article 107</t>
+          <t>Only Lok Sabha MP</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Article 118</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>It includes the powers and privileges of Parliament members.</t>
+          <t>Both Ministers and private members can introduce Constitutional Amendments.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Under normal circumstances, how many sessions of Parliament are held in a year?</t>
+          <t>Which Schedule of the Constitution contains provisions relating to disqualification on the grounds of defection?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9th Schedule</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12th Schedule</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Budget, Monsoon, and Winter Sessions are held annually.</t>
+          <t>10th Schedule deals with anti-defection law as added by the 52nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>How many members can the President nominate to Lok Sabha from Anglo-Indian community (until removed)?</t>
+          <t>The quorum for a meeting of either House of Parliament is?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1/5th</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1/4th</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1/6th</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1/10th</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1/10th</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Till the 104th Amendment (2020), President could nominate 2 Anglo-Indians.</t>
+          <t>The minimum number of members required to hold a meeting is 1/10th of the total strength.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which motion is used to express disapproval of a specific policy of the government?</t>
+          <t>Who can introduce an ordinary bill in Parliament?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No-confidence motion</t>
+          <t>Only Minister</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Censure motion</t>
+          <t>Only MP from ruling party</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cut motion</t>
+          <t>Only Lok Sabha MP</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Censure motion</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>It expresses strong disapproval of a specific policy.</t>
+          <t>Ordinary Bills can be introduced by any MP.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which article mentions the composition of Parliament?</t>
+          <t>The Parliament can legislate on a subject in the State List if</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>Rajya Sabha passes a resolution</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>There is national emergency</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Article 81</t>
+          <t>States request it</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Article 82</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Article 79 states that Parliament consists of President, Lok Sabha, and Rajya Sabha.</t>
+          <t>All these are valid conditions under which Parliament can legislate on State subjects.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a function of Parliament?</t>
+          <t>The maximum number of nominated members in Rajya Sabha is?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Law-making</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Amending Constitution</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Controlling Executive</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Electing President</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Electing President</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>President is elected by an electoral college, not Parliament alone.</t>
+          <t>The President can nominate 12 members with special knowledge in fields like art, literature, etc.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Who can introduce a bill for Constitutional Amendment?</t>
+          <t>Which body recommends disqualification of members on grounds of defection?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Only Ministers</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Only Lok Sabha MP</t>
+          <t>Speaker/Chairman</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2301,662 +2285,670 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Speaker/Chairman</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Both Ministers and private members can introduce Constitutional Amendments.</t>
+          <t>Presiding officer decides on disqualification under anti-defection law.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which article empowers the Parliament to make laws on State List under certain circumstances?</t>
+          <t>The Rajya Sabha can delay an ordinary bill by maximum of</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Article 263</t>
+          <t>1 month</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Article 312</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Under Article 249, Rajya Sabha can pass a resolution allowing Parliament to legislate on State List.</t>
+          <t>Rajya Sabha can delay an ordinary bill for maximum 6 months.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Who is the custodian of the Lok Sabha?</t>
+          <t>Which of the following bills cannot be introduced in Rajya Sabha?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Constitution Amendment Bill</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Financial Bill (Type II)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>The Speaker is the guardian and controller of Lok Sabha.</t>
+          <t>Only Lok Sabha can introduce a Money Bill.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The first hour of every parliamentary sitting is reserved for:</t>
+          <t>In case of a deadlock between the two Houses, how is the issue resolved?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>President’s Rule</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Debate</t>
+          <t>Prime Minister’s veto</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Question Hour</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Private member bill</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Question Hour</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>It is devoted to questions and answers.</t>
+          <t>A joint sitting of Parliament is called under Article 108.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What is the maximum time limit within which Parliament must approve a Money Bill after it is introduced?</t>
+          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>75 days</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>Lok Sabha Speaker</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Prime Minister</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Money Bill must be passed within 14 days by both Houses.</t>
+          <t>The Speaker of the Lok Sabha presides over joint sittings.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a type of bill in Indian Parliament?</t>
+          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Appropriation Bill</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Judicial Bill</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Judicial Bill</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>There’s no such category; only legislative, money, financial bills exist.</t>
+          <t>He presides over joint sittings under Article 108.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The maximum gap between two sessions of Parliament cannot be more than</t>
+          <t>Which of the following is not a part of the Indian Parliament?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4 months</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>According to the Constitution, there must not be a gap of more than 6 months.</t>
+          <t>The Supreme Court is part of the Judiciary, not the Parliament.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Who can introduce a Private Member Bill?</t>
+          <t>Who decides whether a bill is a Money Bill or not?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Only opposition MPs</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Any non-minister MP</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Only ruling party MP</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Only nominated MPs</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Any non-minister MP</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Private Member Bills are introduced by MPs who are not Ministers.</t>
+          <t>The Speaker’s decision on Money Bill is final under Article 110.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>How many members of Anglo-Indian community could be nominated to Lok Sabha (before 104th Amendment)?</t>
+          <t>Who decides whether a Bill is a Money Bill or not?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Earlier, President could nominate 2 Anglo-Indians (now discontinued after 104th Amendment).</t>
+          <t>Speaker’s decision is final under Article 110.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which of the following statements is true regarding the dissolution of Rajya Sabha?</t>
+          <t>What is the current maximum strength of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>It is dissolved every 5 years</t>
+          <t>245</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>It is dissolved by the President</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>It is dissolved by the Prime Minister</t>
+          <t>238</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>It cannot be dissolved</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>It cannot be dissolved</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent house and is not subject to dissolution.</t>
+          <t>Rajya Sabha can have up to 250 members, out of which 12 are nominated.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which House is considered the Council of States?</t>
+          <t>Who can disqualify a Member of Parliament on grounds of defection?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vidhan Sabha</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>Speaker or Chairman</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Election Commission</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Speaker or Chairman</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Rajya Sabha represents the states and is called the Council of States.</t>
+          <t>They decide disqualification under the 10th Schedule.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which of the following is a permanent House?</t>
+          <t>Which of the following statements is true about Private Member’s Bill?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Introduced only by ministers</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Introduced only in Lok Sabha</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Legislative Assembly</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>Introduced by any MP not a minister</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Requires President’s assent first</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Introduced by any MP not a minister</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Rajya Sabha is not subject to dissolution; one-third members retire every 2 years.</t>
+          <t>Private Members are MPs who are not part of the executive.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which of the following statements is true regarding Zero Hour?</t>
+          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>It is mentioned in Constitution</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>It starts at 11 AM</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>It starts after lunch</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>It is a parliamentary convention</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>It is a parliamentary convention</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Zero Hour is not in the rulebook, it's a practice started in 1962.</t>
+          <t>The Vice President of India is the ex-officio Chairman of Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>In case of a deadlock between the two Houses, the President can summon a joint sitting under which article?</t>
+          <t>Which motion is used to express disapproval of a specific policy of the government?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Article 108</t>
+          <t>No-confidence motion</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Censure motion</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Article 111</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Article 112</t>
+          <t>Cut motion</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Article 108</t>
+          <t>Censure motion</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Joint sitting can be called to resolve deadlock between Houses.</t>
+          <t>It expresses strong disapproval of a specific policy.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What is the maximum gap allowed between two parliamentary sessions?</t>
+          <t>Who decides whether a bill is a Money Bill or not?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4 months</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>5 months</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Parliament must meet at least once every six months.</t>
+          <t>As per Article 110, the Speaker's decision is final.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which motion is used to reduce the amount of a demand for grant?</t>
+          <t>Which House of Parliament has special powers regarding creation of All-India Services?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cut Motion</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>No-Confidence Motion</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Censure Motion</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Privilege Motion</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cut Motion</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Cut motions are used to oppose specific provisions in the budget.</t>
+          <t>Rajya Sabha can pass a resolution to create All-India Services.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Speaker of Lok Sabha is elected by</t>
+          <t>Which article provides for the privileges of Parliament members?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Lok Sabha members</t>
+          <t>Article 108</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lok Sabha members</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Speaker is elected by members of Lok Sabha from among themselves.</t>
+          <t>This article grants MPs certain privileges and immunities.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A bill becomes a law only after it is signed by</t>
+          <t>The power to summon or prorogue Parliament rests with</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Vice President</t>
-        </is>
-      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>Prime Minister</t>
@@ -2964,7 +2956,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2974,589 +2966,589 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>President’s assent is essential for a bill to become a law.</t>
+          <t>President summons and prorogues the Parliament on advice of Council of Ministers.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>What is the minimum age to become a member of Rajya Sabha?</t>
+          <t>Which of the following statements is true regarding Zero Hour?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>25 years</t>
+          <t>It is mentioned in Constitution</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>30 years</t>
+          <t>It starts at 11 AM</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>35 years</t>
+          <t>It starts after lunch</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>21 years</t>
+          <t>It is a parliamentary convention</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>30 years</t>
+          <t>It is a parliamentary convention</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>A candidate must be at least 30 years old to be elected to Rajya Sabha.</t>
+          <t>Zero Hour is not in the rulebook, it's a practice started in 1962.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>What is the tenure of the members of the Rajya Sabha?</t>
+          <t>Which of the following is not a function of Parliament?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Executive appointments</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Till dissolved</t>
+          <t>Amending Constitution</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>One-third members retire every 2 years.</t>
+          <t>Judicial review is the function of courts, not Parliament.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The motion to remove the Vice President must be introduced in</t>
+          <t>What is the term of a Rajya Sabha member?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>President’s Office</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>7 years</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Removal motion of Vice President must originate in Rajya Sabha.</t>
+          <t>Rajya Sabha members have a term of 6 years, with one-third retiring every two years.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which schedule of the Constitution deals with allocation of seats in Rajya Sabha?</t>
+          <t>Which of the following is NOT a part of Parliament?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fourth</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sixth</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fourth</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>The Fourth Schedule allocates seats in Rajya Sabha to states and UTs.</t>
+          <t>He is part of Judiciary, not Legislature.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which House of Parliament can initiate impeachment of the President?</t>
+          <t>Under normal circumstances, how many sessions of Parliament are held in a year?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lok Sabha only</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Rajya Sabha only</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Both Houses can initiate impeachment independently.</t>
+          <t>Budget, Monsoon, and Winter Sessions are held annually.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Rajya Sabha can delay an ordinary bill by maximum of</t>
+          <t>Who presides over the joint sitting of Parliament?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Rajya Sabha can delay an ordinary bill for maximum 6 months.</t>
+          <t>In joint sittings, the Speaker of Lok Sabha presides.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>In the event of a conflict between two Houses on an ordinary bill, the mechanism used is</t>
+          <t>In which schedule is the anti-defection law mentioned?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Money Bill clause</t>
+          <t>8th Schedule</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>9th Schedule</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>President’s Order</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Constitutional Amendment</t>
+          <t>11th Schedule</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Joint sitting is used to resolve deadlock on ordinary bills.</t>
+          <t>The 10th Schedule was added by the 52nd Amendment for anti-defection.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Who decides whether a Bill is a Money Bill or not?</t>
+          <t>Which of the following statements is true regarding the dissolution of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>It is dissolved every 5 years</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>It is dissolved by the President</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>It is dissolved by the Prime Minister</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>It cannot be dissolved</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>It cannot be dissolved</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Speaker’s decision is final under Article 110.</t>
+          <t>Rajya Sabha is a permanent house and is not subject to dissolution.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>How many types of major parliamentary committees exist in India?</t>
+          <t>The concept of Parliamentary Privileges in India is taken from which country?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Standing and Ad-hoc are the two main types.</t>
+          <t>India borrowed Parliamentary Privileges from the British system.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Can Rajya Sabha be dissolved?</t>
+          <t>Which of the following motions can lead to the fall of the Council of Ministers?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Yes, every 6 years</t>
+          <t>Calling Attention Motion</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Yes, every 5 years</t>
+          <t>Adjournment Motion</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Censure Motion</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Yes, at the discretion of President</t>
+          <t>No-confidence Motion</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No-confidence Motion</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
+          <t>It expresses loss of confidence in the government.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which committee is called the “watchdog of public purse”?</t>
+          <t>What is the quorum of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>15 members</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>1/6th of total</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Committee on Subordinate Legislation</t>
+          <t>1/10th of total</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Committee on Public Undertakings</t>
+          <t>50 members</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>1/10th of total</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>It ensures accountability in public spending.</t>
+          <t>Minimum 1/10th of the total strength is required to conduct business.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What is the quorum to conduct a sitting of either House of Parliament?</t>
+          <t>The first hour of every parliamentary sitting is reserved for:</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1/5th of total membership</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1/10th of total membership</t>
+          <t>Debate</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1/3rd of total membership</t>
+          <t>Question Hour</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Half the total strength</t>
+          <t>Private member bill</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1/10th of total membership</t>
+          <t>Question Hour</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Quorum is 1/10th of total strength of the House.</t>
+          <t>It is devoted to questions and answers.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which of the following motions can lead to the fall of the Council of Ministers?</t>
+          <t>How many members can be nominated to the Rajya Sabha by the President?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Calling Attention Motion</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Adjournment Motion</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Censure Motion</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>No-confidence Motion</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>No-confidence Motion</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>It expresses loss of confidence in the government.</t>
+          <t>The President can nominate 12 members to Rajya Sabha from fields like art, science, etc.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The concept of Parliamentary Privileges in India is taken from which country?</t>
+          <t>How many types of major parliamentary committees exist in India?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>India borrowed Parliamentary Privileges from the British system.</t>
+          <t>Standing and Ad-hoc are the two main types.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Who presides over the joint sitting of Parliament?</t>
+          <t>The power to summon or prorogue the Parliament rests with?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>Prime Minister</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Lok Sabha Speaker</t>
-        </is>
-      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>Vice President</t>
@@ -3564,1885 +3556,1893 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>In joint sittings, the Speaker of Lok Sabha presides.</t>
+          <t>The President summons and prorogues Parliament sessions.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which House of Parliament is considered more powerful in terms of money matters?</t>
+          <t>In the event of a conflict between two Houses on an ordinary bill, the mechanism used is</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Money Bill clause</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Both equal</t>
+          <t>President’s Order</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Constitutional Amendment</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Money Bills can only be introduced and passed in the Lok Sabha.</t>
+          <t>Joint sitting is used to resolve deadlock on ordinary bills.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Money Bills can be introduced only in which House?</t>
+          <t>Which of the following is true about Zero Hour?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>It is mentioned in Constitution</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>It begins at 12 noon</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Either House</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
+          <t>It is a procedural motion</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>It is started by Rajya Sabha</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>It begins at 12 noon</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Only Lok Sabha can introduce a Money Bill as per Article 110.</t>
+          <t>Zero Hour starts at 12 PM and is an Indian innovation (not in Constitution).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which of the following motions is NOT related to financial matters?</t>
+          <t>The maximum gap between two sessions of Parliament cannot be more than</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cut Motion</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Adjournment Motion</t>
+          <t>4 months</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Appropriation Bill</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Finance Bill</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Adjournment Motion</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>It is used to draw attention to urgent matters, not financial matters.</t>
+          <t>According to the Constitution, there must not be a gap of more than 6 months.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which authority decides the disqualification of MPs under anti-defection?</t>
+          <t>How many members can the President nominate to Lok Sabha from Anglo-Indian community (until removed)?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Speaker/Chairman</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Speaker/Chairman</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>The Presiding Officer decides under 10th Schedule.</t>
+          <t>Till the 104th Amendment (2020), President could nominate 2 Anglo-Indians.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>What is the maximum tenure of Lok Sabha?</t>
+          <t>Can Rajya Sabha be dissolved?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>3 years</t>
+          <t>Yes, every 6 years</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Yes, every 5 years</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Yes, at the discretion of President</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Lok Sabha has a normal term of 5 years unless dissolved earlier.</t>
+          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The Parliament can legislate on a subject in the State List if</t>
+          <t>Which article of the Constitution deals with the composition of the Parliament?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rajya Sabha passes a resolution</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>There is national emergency</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>States request it</t>
+          <t>Article 81</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>All these are valid conditions under which Parliament can legislate on State subjects.</t>
+          <t>Article 79 defines the structure of the Indian Parliament.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Can the Rajya Sabha be dissolved?</t>
+          <t>Money Bill can be introduced only in</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Yes, after 6 years</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Yes, by the President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Only in emergency</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
+          <t>Money Bills can be introduced only in Lok Sabha, as per Article 110.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which of the following bills cannot be introduced in Rajya Sabha?</t>
+          <t>What happens if there is a deadlock on a Constitutional Amendment Bill?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>Joint Sitting is held</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>President decides</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Constitution Amendment Bill</t>
+          <t>Lok Sabha prevails</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Financial Bill (Type II)</t>
+          <t>Bill fails</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Bill fails</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Only Lok Sabha can introduce a Money Bill.</t>
+          <t>There is no provision for joint sitting on Constitutional Amendments.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which article empowers Parliament to create new states?</t>
+          <t>Who can introduce a Private Member Bill?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Article 2</t>
+          <t>Only opposition MPs</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>Any non-minister MP</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Article 1</t>
+          <t>Only ruling party MP</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Article 5</t>
+          <t>Only nominated MPs</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>Any non-minister MP</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Parliament can form new states or alter existing ones.</t>
+          <t>Private Member Bills are introduced by MPs who are not Ministers.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
+          <t>What is the tenure of the Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Till next election</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Till he/she resigns or removed</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Till he/she resigns or removed</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>As per Article 64, Vice President is ex-officio Chairman of Rajya Sabha.</t>
+          <t>Speaker holds office until removed or resignation, even after dissolution.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which of the following is true about Zero Hour?</t>
+          <t>The first sitting of the Constituent Assembly took place in which year?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>It is mentioned in Constitution</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>It begins at 12 noon</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>It is a procedural motion</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>It is started by Rajya Sabha</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>It begins at 12 noon</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Zero Hour starts at 12 PM and is an Indian innovation (not in Constitution).</t>
+          <t>The Constituent Assembly first met on 9 December 1946.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which House of Parliament has special powers regarding creation of All-India Services?</t>
+          <t>Which of the following statements is correct regarding Money Bill?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>It needs approval of Rajya Sabha</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Rajya Sabha can reject it</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
+          <t>Rajya Sabha can suggest amendments</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Rajya Sabha can amend it</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Rajya Sabha can suggest amendments</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Rajya Sabha can pass a resolution to create All-India Services.</t>
+          <t>Rajya Sabha can only suggest, not amend or reject it.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which article provides for the privileges of Parliament members?</t>
+          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Article 108</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>This article grants MPs certain privileges and immunities.</t>
+          <t>As per Article 64, Vice President is ex-officio Chairman of Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>The power to summon or prorogue Parliament rests with</t>
+          <t>What is the maximum strength of the Lok Sabha as per the Constitution?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>530</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>545</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>552</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>560</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>President summons and prorogues the Parliament on advice of Council of Ministers.</t>
+          <t>As per Article 81, the maximum strength is 552 members.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which Article deals with the procedure in financial matters like Budget?</t>
+          <t>What is the quorum to constitute a meeting of the Lok Sabha?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Article 109</t>
+          <t>1/2 of total members</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>1/10 of total members</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Article 112</t>
+          <t>1/5 of total members</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>1/4 of total members</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>1/10 of total members</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>It governs financial bills other than money bills.</t>
+          <t>Quorum is the minimum number of members required to hold a sitting.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which constitutional amendment lowered the voting age from 21 to 18?</t>
+          <t>Which article of the Constitution defines a Money Bill?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>42nd</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>44th</t>
+          <t>Article 112</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>61st</t>
+          <t>Article 113</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>52nd</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>61st</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>The 61st Amendment Act, 1989, reduced the voting age.</t>
+          <t>This article gives the definition of a Money Bill.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>What is the maximum time Rajya Sabha can hold a Money Bill?</t>
+          <t>Which Article allows the Parliament to make laws on a matter in the State List under national interest?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>7 days</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>21 days</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Rajya Sabha must return a Money Bill within 14 days; else it is deemed passed.</t>
+          <t>Rajya Sabha can authorize Parliament to legislate on State List in national interest.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which body recommends disqualification of members on grounds of defection?</t>
+          <t>Which of the following statements is incorrect regarding the Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>He/she can vote in first instance</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Speaker/Chairman</t>
+          <t>He/she is elected from among Lok Sabha members</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>He/she can disqualify a member under anti-defection law</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>He/she is subordinate to the President</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Speaker/Chairman</t>
+          <t>He/she is subordinate to the President</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Presiding officer decides on disqualification under anti-defection law.</t>
+          <t>Speaker is not subordinate to anyone; he is the constitutional authority.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>In case of a deadlock between the two Houses, how is the issue resolved?</t>
+          <t>What is the difference between adjournment and prorogation?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>President’s Rule</t>
+          <t>No difference</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Prime Minister’s veto</t>
+          <t>Adjournment by President, Prorogation by Speaker</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Adjournment is for a short period, Prorogation ends session</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Adjournment ends the House</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Adjournment is for a short period, Prorogation ends session</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>A joint sitting of Parliament is called under Article 108.</t>
+          <t>Adjournment is temporary; prorogation ends a session.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which of the following statements is incorrect regarding the Speaker of Lok Sabha?</t>
+          <t>How many times can the President summon Parliament in a year at minimum?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>He/she can vote in first instance</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>He/she is elected from among Lok Sabha members</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>He/she can disqualify a member under anti-defection law</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>He/she is subordinate to the President</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>He/she is subordinate to the President</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Speaker is not subordinate to anyone; he is the constitutional authority.</t>
+          <t>There must be at least two sessions in a year as per Article 85.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>How many houses does the Indian Parliament consist of?</t>
+          <t>What is the maximum time Rajya Sabha can hold a Money Bill?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>One</t>
+          <t>7 days</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Two</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Three</t>
+          <t>21 days</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Four</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Two</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>The Indian Parliament has two houses – Lok Sabha and Rajya Sabha.</t>
+          <t>Rajya Sabha must return a Money Bill within 14 days; else it is deemed passed.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
+          <t>Which House of Parliament is considered more powerful in terms of money matters?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
+          <t>Both equal</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Vice President</t>
-        </is>
-      </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>The Vice President of India is the ex-officio Chairman of Rajya Sabha.</t>
+          <t>Money Bills can only be introduced and passed in the Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Who decides whether a bill is a Money Bill or not?</t>
+          <t>Which House of Parliament can initiate impeachment of the President?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Lok Sabha only</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Rajya Sabha only</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>As per Article 110, the Speaker's decision is final.</t>
+          <t>Both Houses can initiate impeachment independently.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>What happens if there is a deadlock on a Constitutional Amendment Bill?</t>
+          <t>Which article empowers the Parliament to make laws on State List under certain circumstances?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Joint Sitting is held</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>President decides</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lok Sabha prevails</t>
+          <t>Article 263</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bill fails</t>
+          <t>Article 312</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bill fails</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>There is no provision for joint sitting on Constitutional Amendments.</t>
+          <t>Under Article 249, Rajya Sabha can pass a resolution allowing Parliament to legislate on State List.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Which Article empowers the Parliament to make laws on State List during emergency?</t>
+          <t>Can a non-member of Parliament become a minister?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Yes, for 3 months</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Article 248</t>
+          <t>Yes, for 1 year</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Parliament can legislate on state subjects during National Emergency under Article 250.</t>
+          <t>He must get elected to either House within 6 months.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Which of the following is not a function of Parliament?</t>
+          <t>Which is not required to pass a Constitutional Amendment Bill?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>Simple Majority</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Executive appointments</t>
+          <t>Special Majority</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Ratification by States</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Amending Constitution</t>
+          <t>President's assent</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Simple Majority</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Judicial review is the function of courts, not Parliament.</t>
+          <t>Most Constitutional Amendments require special majority, not simple majority.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>The maximum strength of the Lok Sabha is</t>
+          <t>In case of a deadlock between the two Houses, the President can summon a joint sitting under which article?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>Article 108</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>Article 111</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>Article 112</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>Article 108</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>According to Article 81, the Lok Sabha can have up to 552 members.</t>
+          <t>Joint sitting can be called to resolve deadlock between Houses.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>What is the current maximum strength of Rajya Sabha?</t>
+          <t>Money Bills can be introduced only in which House?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
+          <t>Either House</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Rajya Sabha can have up to 250 members, out of which 12 are nominated.</t>
+          <t>Only Lok Sabha can introduce a Money Bill as per Article 110.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>What is the term of nominated members of Rajya Sabha?</t>
+          <t>Which of the following is not a function of Parliament?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2 years</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Amending the Constitution</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Electing the President</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Enforcing laws</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Enforcing laws</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Like elected members, nominated members also serve for 6 years.</t>
+          <t>Enforcing laws is the function of the executive.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which article of the Constitution deals with the composition of the Parliament?</t>
+          <t>Which session of Parliament is usually held from February to May?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Monsoon Session</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>Winter Session</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Article 81</t>
+          <t>Budget Session</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Special Session</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>Budget Session</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Article 79 defines the structure of the Indian Parliament.</t>
+          <t>It usually begins in February and includes the budget presentation.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>How many times can the President summon Parliament in a year at minimum?</t>
+          <t>Can the Rajya Sabha be dissolved?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes, after 6 years</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Yes, by the President</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Only in emergency</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>There must be at least two sessions in a year as per Article 85.</t>
+          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>The quorum for a meeting of either House of Parliament is?</t>
+          <t>Which of the following is NOT true about Rajya Sabha?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1/5th</t>
+          <t>It is a permanent House</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1/4th</t>
+          <t>It has equal powers with Lok Sabha on Money Bills</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1/6th</t>
+          <t>It represents states</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1/10th</t>
+          <t>It has 250 members</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1/10th</t>
+          <t>It has equal powers with Lok Sabha on Money Bills</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>The minimum number of members required to hold a meeting is 1/10th of the total strength.</t>
+          <t>Rajya Sabha has limited role in Money Bills.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Which Schedule of the Constitution contains provisions relating to disqualification on the grounds of defection?</t>
+          <t>Which of the following is NOT a function of Parliament?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>Law-making</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>9th Schedule</t>
+          <t>Amending Constitution</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Controlling Executive</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>12th Schedule</t>
+          <t>Electing President</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Electing President</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>10th Schedule deals with anti-defection law as added by the 52nd Amendment.</t>
+          <t>President is elected by an electoral college, not Parliament alone.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Money Bill can be introduced only in</t>
+          <t>How many members of Anglo-Indian community could be nominated to Lok Sabha (before 104th Amendment)?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Money Bills can be introduced only in Lok Sabha, as per Article 110.</t>
+          <t>Earlier, President could nominate 2 Anglo-Indians (now discontinued after 104th Amendment).</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which House of Parliament is not subject to dissolution?</t>
+          <t>Which Article authorizes Parliament to make laws on State List during national emergency?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
+          <t>Article 252</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Article 253</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent House, not subject to dissolution.</t>
+          <t>During National Emergency, Parliament can legislate on State subjects under Article 250.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>How many readings does a bill go through in the Parliament?</t>
+          <t>In which year was the Parliament House of India inaugurated?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Each House of Parliament conducts 3 readings: introduction, consideration, and passing.</t>
+          <t>The current Parliament House was inaugurated in 1927 by Lord Irwin.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Which Article empowers Parliament to create new states?</t>
+          <t>The motion to remove the Vice President must be introduced in</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Article 2</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Article 4</t>
+          <t>President’s Office</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Article 5</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>It gives Parliament power to create or alter state boundaries.</t>
+          <t>Removal motion of Vice President must originate in Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Which Committee examines the report of the Comptroller and Auditor General (CAG)?</t>
+          <t>What is the minimum age to become a member of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>25 years</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Privileges Committee</t>
+          <t>35 years</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Business Advisory Committee</t>
+          <t>21 years</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>PAC examines CAG reports and ensures public money is spent properly.</t>
+          <t>A candidate must be at least 30 years old to be elected to Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>In which case did the Supreme Court rule that Parliament cannot alter the Basic Structure?</t>
+          <t>How many houses does the Indian Parliament consist of?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Minerva Mills v. Union of India</t>
+          <t>One</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Golak Nath v. State of Punjab</t>
+          <t>Two</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati v. State of Kerala</t>
+          <t>Three</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SR Bommai v. Union of India</t>
+          <t>Four</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati v. State of Kerala</t>
+          <t>Two</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>This judgment introduced the Basic Structure doctrine.</t>
+          <t>The Indian Parliament has two houses – Lok Sabha and Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
+          <t>What is the maximum tenure of Lok Sabha?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>The Speaker of the Lok Sabha presides over joint sittings.</t>
+          <t>Lok Sabha has a normal term of 5 years unless dissolved earlier.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>What is the term of a Rajya Sabha member?</t>
+          <t>Which House has more power in the case of a Money Bill?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Both equal</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>7 years</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Rajya Sabha members have a term of 6 years, with one-third retiring every two years.</t>
+          <t>Rajya Sabha can only make recommendations on Money Bills.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Which session of Parliament is usually held from February to May?</t>
+          <t>Which provision ensures that Parliament remains sovereign in making laws?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Monsoon Session</t>
+          <t>Doctrine of pith and substance</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Winter Session</t>
+          <t>Basic structure</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Budget Session</t>
+          <t>Separation of powers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Special Session</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Budget Session</t>
+          <t>Doctrine of pith and substance</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>It usually begins in February and includes the budget presentation.</t>
+          <t>It gives Parliament flexibility in legislative matters.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Which of the following is not a parliamentary committee?</t>
+          <t>The maximum strength of the Lok Sabha is</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>545</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>552</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Committee on Petitions</t>
+          <t>560</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Cabinet Committees are executive, not parliamentary.</t>
+          <t>According to Article 81, the Lok Sabha can have up to 552 members.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which Article provides for the privileges of Parliament?</t>
+          <t>Which Article mentions the composition of the Rajya Sabha?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Article 104</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>Article 81</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Article 106</t>
+          <t>Article 82</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Article 83</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>It provides for the powers, privileges and immunities of Parliament and its members.</t>
+          <t>Article 80 of the Constitution deals with the composition of Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Which Article allows the Parliament to make laws on a matter in the State List under national interest?</t>
+          <t>Which article empowers Parliament to create new states?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>Article 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Article 1</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>Article 5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Rajya Sabha can authorize Parliament to legislate on State List in national interest.</t>
+          <t>Parliament can form new states or alter existing ones.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>The maximum number of nominated members in Rajya Sabha is?</t>
+          <t>Who is the custodian of the Lok Sabha?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>The President can nominate 12 members with special knowledge in fields like art, literature, etc.</t>
+          <t>The Speaker is the guardian and controller of Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which article of the Constitution defines a Money Bill?</t>
+          <t>Which committee is called the “watchdog of public purse”?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Article 112</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Article 113</t>
+          <t>Committee on Subordinate Legislation</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>Committee on Public Undertakings</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>This article gives the definition of a Money Bill.</t>
+          <t>It ensures accountability in public spending.</t>
         </is>
       </c>
     </row>

--- a/Data/IPParliament.xlsx
+++ b/Data/IPParliament.xlsx
@@ -472,927 +472,923 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a type of bill in Indian Parliament?</t>
+          <t>Who is the custodian of the Lok Sabha?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Appropriation Bill</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Judicial Bill</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Judicial Bill</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>There’s no such category; only legislative, money, financial bills exist.</t>
+          <t>The Speaker is the guardian and controller of Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What happens if there is a vacancy in the office of Speaker and Deputy Speaker of Lok Sabha?</t>
+          <t>Which article mentions the composition of Parliament?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>President presides over</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Prime Minister presides over</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Member appointed by President presides</t>
+          <t>Article 81</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Any member appointed by the House presides</t>
+          <t>Article 82</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Any member appointed by the House presides</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The House appoints a member to preside in absence of Speaker/Deputy Speaker.</t>
+          <t>Article 79 states that Parliament consists of President, Lok Sabha, and Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which of the following motions needs the support of at least 50 members to be admitted in Lok Sabha?</t>
+          <t>Which of the following statements is true regarding the dissolution of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>It is dissolved every 5 years</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>No-confidence motion</t>
+          <t>It is dissolved by the President</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Censure motion</t>
+          <t>It is dissolved by the Prime Minister</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Privilege motion</t>
+          <t>It cannot be dissolved</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>It cannot be dissolved</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>It needs support of 50 members for admission.</t>
+          <t>Rajya Sabha is a permanent house and is not subject to dissolution.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which schedule of the Constitution contains the Anti-Defection Law?</t>
+          <t>Which article of the Constitution defines a Money Bill?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8th</t>
+          <t>Article 112</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>Article 113</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>The Tenth Schedule deals with provisions regarding disqualification on the grounds of defection.</t>
+          <t>This article gives the definition of a Money Bill.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The term ‘Zero Hour’ refers to</t>
+          <t>Which article of the Constitution deals with the composition of the Parliament?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>First hour after lunch</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Time before Question Hour</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Time immediately after Question Hour</t>
+          <t>Article 81</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Time after adjournment</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Time immediately after Question Hour</t>
+          <t>Article 79</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Zero Hour is an Indian innovation, used to raise urgent matters.</t>
+          <t>Article 79 defines the structure of the Indian Parliament.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What is the tenure of the members of the Rajya Sabha?</t>
+          <t>Which of the following motions needs the support of at least 50 members to be admitted in Lok Sabha?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>No-confidence motion</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Censure motion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Till dissolved</t>
+          <t>Privilege motion</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>One-third members retire every 2 years.</t>
+          <t>It needs support of 50 members for admission.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which Article deals with the procedure in financial matters like Budget?</t>
+          <t>In which case did the Supreme Court rule that Parliament cannot alter the Basic Structure?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Article 109</t>
+          <t>Minerva Mills v. Union of India</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Golak Nath v. State of Punjab</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Article 112</t>
+          <t>Keshavananda Bharati v. State of Kerala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>SR Bommai v. Union of India</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>Keshavananda Bharati v. State of Kerala</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>It governs financial bills other than money bills.</t>
+          <t>This judgment introduced the Basic Structure doctrine.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The first Speaker of Lok Sabha was</t>
+          <t>The maximum number of nominated members in Rajya Sabha is?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>G V Mavalankar</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>M A Ayyangar</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S Radhakrishnan</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>G V Mavalankar</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>He was the first Speaker of Lok Sabha after 1952 elections.</t>
+          <t>The President can nominate 12 members with special knowledge in fields like art, literature, etc.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which article mentions the composition of Parliament?</t>
+          <t>Which of the following is NOT a function of Parliament?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>Law-making</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Amending Constitution</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Article 81</t>
+          <t>Controlling Executive</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Article 82</t>
+          <t>Electing President</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>Electing President</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Article 79 states that Parliament consists of President, Lok Sabha, and Rajya Sabha.</t>
+          <t>President is elected by an electoral college, not Parliament alone.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which of the following is not a parliamentary committee?</t>
+          <t>Which committee is called the “watchdog of public purse”?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Estimates Committee</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>Public Accounts Committee</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Estimates Committee</t>
-        </is>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>Committee on Subordinate Legislation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Committee on Petitions</t>
+          <t>Committee on Public Undertakings</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Cabinet Committees are executive, not parliamentary.</t>
+          <t>It ensures accountability in public spending.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which Article provides for the privileges of Parliament?</t>
+          <t>In case of deadlock between two Houses on a bill, who summons the joint sitting?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Article 104</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Article 106</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>It provides for the powers, privileges and immunities of Parliament and its members.</t>
+          <t>President summons a joint session to resolve the deadlock.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Under which article can Parliament punish a person for breach of privilege?</t>
+          <t>Which of the following is a permanent House?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Article 107</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Article 118</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Article 124</t>
-        </is>
-      </c>
+          <t>Legislative Assembly</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>It includes the powers and privileges of Parliament members.</t>
+          <t>Rajya Sabha is not subject to dissolution; one-third members retire every 2 years.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which constitutional amendment lowered the voting age from 21 to 18?</t>
+          <t>Which provision ensures that Parliament remains sovereign in making laws?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>42nd</t>
+          <t>Doctrine of pith and substance</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44th</t>
+          <t>Basic structure</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>61st</t>
+          <t>Separation of powers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52nd</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>61st</t>
+          <t>Doctrine of pith and substance</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>The 61st Amendment Act, 1989, reduced the voting age.</t>
+          <t>It gives Parliament flexibility in legislative matters.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which Article empowers Parliament to create new states?</t>
+          <t>What is the minimum age to become a member of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Article 2</t>
+          <t>25 years</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Article 4</t>
+          <t>35 years</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Article 5</t>
+          <t>21 years</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>It gives Parliament power to create or alter state boundaries.</t>
+          <t>A candidate must be at least 30 years old to be elected to Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>What is the maximum gap allowed between two parliamentary sessions?</t>
+          <t>Which article empowers the Parliament to make laws on State List under certain circumstances?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4 months</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5 months</t>
+          <t>Article 263</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Article 312</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Parliament must meet at least once every six months.</t>
+          <t>Under Article 249, Rajya Sabha can pass a resolution allowing Parliament to legislate on State List.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What is the maximum number of members in Rajya Sabha from a single state?</t>
+          <t>The Speaker of Lok Sabha is elected by</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Lok Sabha members</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Lok Sabha members</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Uttar Pradesh sends the highest number (31) to Rajya Sabha.</t>
+          <t>Speaker is elected by members of Lok Sabha from among themselves.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The first Lok Sabha was constituted in</t>
+          <t>Which schedule of the Constitution deals with allocation of seats in Rajya Sabha?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>First</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>Fourth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Sixth</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>Fourth</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>The first Lok Sabha was formed in 1952 after the first general election.</t>
+          <t>The Fourth Schedule allocates seats in Rajya Sabha to states and UTs.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which body examines the annual financial statement laid before Parliament?</t>
+          <t>What is the term of nominated members of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>The Public Accounts Committee examines the audit reports and financial accounts.</t>
+          <t>Like elected members, nominated members also serve for 6 years.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which House is considered the Council of States?</t>
+          <t>Which of the following bills cannot be introduced in Rajya Sabha?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vidhan Sabha</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>Constitution Amendment Bill</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Financial Bill (Type II)</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Rajya Sabha represents the states and is called the Council of States.</t>
+          <t>Only Lok Sabha can introduce a Money Bill.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which schedule of the Constitution deals with allocation of seats in Rajya Sabha?</t>
+          <t>Money Bills can be introduced only in which House?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fourth</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Sixth</t>
-        </is>
-      </c>
+          <t>Either House</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fourth</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>The Fourth Schedule allocates seats in Rajya Sabha to states and UTs.</t>
+          <t>Only Lok Sabha can introduce a Money Bill as per Article 110.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What is the term of nominated members of Rajya Sabha?</t>
+          <t>The maximum gap between two sessions of Parliament cannot be more than</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2 years</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>4 months</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Like elected members, nominated members also serve for 6 years.</t>
+          <t>According to the Constitution, there must not be a gap of more than 6 months.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What is the quorum to conduct a sitting of either House of Parliament?</t>
+          <t>Can the Rajya Sabha be dissolved?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1/5th of total membership</t>
+          <t>Yes, after 6 years</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1/10th of total membership</t>
+          <t>Yes, by the President</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1/3rd of total membership</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Half the total strength</t>
+          <t>Only in emergency</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1/10th of total membership</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Quorum is 1/10th of total strength of the House.</t>
+          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which of the following motions is NOT related to financial matters?</t>
+          <t>Which House has more power in the case of a Money Bill?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cut Motion</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Adjournment Motion</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Appropriation Bill</t>
+          <t>Both equal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Finance Bill</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Adjournment Motion</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>It is used to draw attention to urgent matters, not financial matters.</t>
+          <t>Rajya Sabha can only make recommendations on Money Bills.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which authority decides the disqualification of MPs under anti-defection?</t>
+          <t>Which body recommends disqualification of members on grounds of defection?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1402,419 +1398,427 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Speaker/Chairman</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Supreme Court</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Speaker/Chairman</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Speaker/Chairman</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>The Presiding Officer decides under 10th Schedule.</t>
+          <t>Presiding officer decides on disqualification under anti-defection law.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>In which case did the Supreme Court rule that Parliament cannot alter the Basic Structure?</t>
+          <t>In which year was the Parliament House of India inaugurated?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minerva Mills v. Union of India</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Golak Nath v. State of Punjab</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati v. State of Kerala</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SR Bommai v. Union of India</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati v. State of Kerala</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>This judgment introduced the Basic Structure doctrine.</t>
+          <t>The current Parliament House was inaugurated in 1927 by Lord Irwin.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which Committee examines the report of the Comptroller and Auditor General (CAG)?</t>
+          <t>Which Article mentions the composition of the Rajya Sabha?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>Article 81</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Privileges Committee</t>
+          <t>Article 82</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Business Advisory Committee</t>
+          <t>Article 83</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PAC examines CAG reports and ensures public money is spent properly.</t>
+          <t>Article 80 of the Constitution deals with the composition of Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which of the following is a permanent House?</t>
+          <t>The first hour of every parliamentary sitting is reserved for:</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Debate</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Legislative Assembly</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>Question Hour</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Private member bill</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Question Hour</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Rajya Sabha is not subject to dissolution; one-third members retire every 2 years.</t>
+          <t>It is devoted to questions and answers.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What is the maximum time limit within which Parliament must approve a Money Bill after it is introduced?</t>
+          <t>Under normal circumstances, how many sessions of Parliament are held in a year?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>75 days</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Money Bill must be passed within 14 days by both Houses.</t>
+          <t>Budget, Monsoon, and Winter Sessions are held annually.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>In which year was the Anti-Defection Law added to the Constitution?</t>
+          <t>Which motion is used to express disapproval of a specific policy of the government?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>No-confidence motion</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>Censure motion</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>Adjournment motion</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>Cut motion</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>Censure motion</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>It was added through the 52nd Amendment in 1985.</t>
+          <t>It expresses strong disapproval of a specific policy.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What is the maximum gap between two sessions of Parliament?</t>
+          <t>What is the quorum of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>15 members</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4 months</t>
+          <t>1/6th of total</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>1/10th of total</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>50 members</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>1/10th of total</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>There must not be more than a six-month gap between two sessions.</t>
+          <t>Minimum 1/10th of the total strength is required to conduct business.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Who acts as the pro tem Speaker of Lok Sabha?</t>
+          <t>Which motion is used to reduce the amount of a demand for grant?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Longest-serving MP</t>
+          <t>Cut Motion</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Senior-most member</t>
+          <t>No-Confidence Motion</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Censure Motion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Privilege Motion</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Senior-most member</t>
+          <t>Cut Motion</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>The senior-most member is appointed to conduct the first meeting until Speaker is elected.</t>
+          <t>Cut motions are used to oppose specific provisions in the budget.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which Article empowers the Parliament to make laws on State List during emergency?</t>
+          <t>The Rajya Sabha can delay an ordinary bill by maximum of</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>1 month</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Article 248</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Parliament can legislate on state subjects during National Emergency under Article 250.</t>
+          <t>Rajya Sabha can delay an ordinary bill for maximum 6 months.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which motion is used to reduce the amount of a demand for grant?</t>
+          <t>What is the quorum to constitute a meeting of the Lok Sabha?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cut Motion</t>
+          <t>1/2 of total members</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>No-Confidence Motion</t>
+          <t>1/10 of total members</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Censure Motion</t>
+          <t>1/5 of total members</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Privilege Motion</t>
+          <t>1/4 of total members</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cut Motion</t>
+          <t>1/10 of total members</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Cut motions are used to oppose specific provisions in the budget.</t>
+          <t>Quorum is the minimum number of members required to hold a sitting.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>How many readings does a bill go through in the Parliament?</t>
+          <t>What is the difference between adjournment and prorogation?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No difference</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Adjournment by President, Prorogation by Speaker</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Adjournment is for a short period, Prorogation ends session</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Adjournment ends the House</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Adjournment is for a short period, Prorogation ends session</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Each House of Parliament conducts 3 readings: introduction, consideration, and passing.</t>
+          <t>Adjournment is temporary; prorogation ends a session.</t>
         </is>
       </c>
     </row>
@@ -1824,47 +1828,47 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Speaker of Lok Sabha is elected by</t>
+          <t>The term ‘Zero Hour’ refers to</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>First hour after lunch</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lok Sabha members</t>
+          <t>Time before Question Hour</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Time immediately after Question Hour</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Time after adjournment</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lok Sabha members</t>
+          <t>Time immediately after Question Hour</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Speaker is elected by members of Lok Sabha from among themselves.</t>
+          <t>Zero Hour is an Indian innovation, used to raise urgent matters.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>In case of deadlock between two Houses on a bill, who summons the joint sitting?</t>
+          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1874,263 +1878,267 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>President summons a joint session to resolve the deadlock.</t>
+          <t>The Vice President of India is the ex-officio Chairman of Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a function of the Estimates Committee?</t>
+          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Suggesting economic improvements</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Examining estimates in Budget</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Examining CAG reports</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ensuring efficient allocation</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Examining CAG reports</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>That's the job of Public Accounts Committee, not Estimates Committee.</t>
+          <t>As per Article 64, Vice President is ex-officio Chairman of Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A bill becomes a law only after it is signed by</t>
+          <t>What is the maximum gap between two sessions of Parliament?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>4 months</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>President’s assent is essential for a bill to become a law.</t>
+          <t>There must not be more than a six-month gap between two sessions.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which House of Parliament is not subject to dissolution?</t>
+          <t>What happens if there is a deadlock on a Constitutional Amendment Bill?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Joint Sitting is held</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>President decides</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>Lok Sabha prevails</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bill fails</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Bill fails</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent House, not subject to dissolution.</t>
+          <t>There is no provision for joint sitting on Constitutional Amendments.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Who can introduce a bill for Constitutional Amendment?</t>
+          <t>Which of the following statements is true about Private Member’s Bill?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Only Ministers</t>
+          <t>Introduced only by ministers</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Only Lok Sabha MP</t>
+          <t>Introduced only in Lok Sabha</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Introduced by any MP not a minister</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Requires President’s assent first</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Introduced by any MP not a minister</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Both Ministers and private members can introduce Constitutional Amendments.</t>
+          <t>Private Members are MPs who are not part of the executive.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which Schedule of the Constitution contains provisions relating to disqualification on the grounds of defection?</t>
+          <t>In case of a deadlock between the two Houses, the President can summon a joint sitting under which article?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>Article 108</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9th Schedule</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Article 111</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>12th Schedule</t>
+          <t>Article 112</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Article 108</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>10th Schedule deals with anti-defection law as added by the 52nd Amendment.</t>
+          <t>Joint sitting can be called to resolve deadlock between Houses.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The quorum for a meeting of either House of Parliament is?</t>
+          <t>Which of the following statements is correct regarding Money Bill?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1/5th</t>
+          <t>It needs approval of Rajya Sabha</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1/4th</t>
+          <t>Rajya Sabha can reject it</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1/6th</t>
+          <t>Rajya Sabha can suggest amendments</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1/10th</t>
+          <t>Rajya Sabha can amend it</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1/10th</t>
+          <t>Rajya Sabha can suggest amendments</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>The minimum number of members required to hold a meeting is 1/10th of the total strength.</t>
+          <t>Rajya Sabha can only suggest, not amend or reject it.</t>
         </is>
       </c>
     </row>
@@ -2140,1233 +2148,1233 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Who can introduce an ordinary bill in Parliament?</t>
+          <t>What is the maximum tenure of Lok Sabha?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Only Minister</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Only MP from ruling party</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Only Lok Sabha MP</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Ordinary Bills can be introduced by any MP.</t>
+          <t>Lok Sabha has a normal term of 5 years unless dissolved earlier.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Parliament can legislate on a subject in the State List if</t>
+          <t>In case of a deadlock between the two Houses, how is the issue resolved?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rajya Sabha passes a resolution</t>
+          <t>President’s Rule</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>There is national emergency</t>
+          <t>Prime Minister’s veto</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>States request it</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>All these are valid conditions under which Parliament can legislate on State subjects.</t>
+          <t>A joint sitting of Parliament is called under Article 108.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The maximum number of nominated members in Rajya Sabha is?</t>
+          <t>Who decides whether a Bill is a Money Bill or not?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>The President can nominate 12 members with special knowledge in fields like art, literature, etc.</t>
+          <t>Speaker’s decision is final under Article 110.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which body recommends disqualification of members on grounds of defection?</t>
+          <t>In which schedule is the anti-defection law mentioned?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>8th Schedule</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Speaker/Chairman</t>
+          <t>9th Schedule</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>11th Schedule</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Speaker/Chairman</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Presiding officer decides on disqualification under anti-defection law.</t>
+          <t>The 10th Schedule was added by the 52nd Amendment for anti-defection.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Rajya Sabha can delay an ordinary bill by maximum of</t>
+          <t>Which session of Parliament is usually held from February to May?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Monsoon Session</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Winter Session</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>Budget Session</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>Special Session</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Budget Session</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Rajya Sabha can delay an ordinary bill for maximum 6 months.</t>
+          <t>It usually begins in February and includes the budget presentation.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which of the following bills cannot be introduced in Rajya Sabha?</t>
+          <t>How many members of Anglo-Indian community could be nominated to Lok Sabha (before 104th Amendment)?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Constitution Amendment Bill</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Financial Bill (Type II)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Only Lok Sabha can introduce a Money Bill.</t>
+          <t>Earlier, President could nominate 2 Anglo-Indians (now discontinued after 104th Amendment).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>In case of a deadlock between the two Houses, how is the issue resolved?</t>
+          <t>What happens if there is a vacancy in the office of Speaker and Deputy Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>President’s Rule</t>
+          <t>President presides over</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Prime Minister’s veto</t>
+          <t>Prime Minister presides over</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Member appointed by President presides</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Any member appointed by the House presides</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Any member appointed by the House presides</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>A joint sitting of Parliament is called under Article 108.</t>
+          <t>The House appoints a member to preside in absence of Speaker/Deputy Speaker.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
+          <t>Which of the following statements is incorrect regarding the Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>He/she can vote in first instance</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>He/she is elected from among Lok Sabha members</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>He/she can disqualify a member under anti-defection law</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>He/she is subordinate to the President</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>He/she is subordinate to the President</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>The Speaker of the Lok Sabha presides over joint sittings.</t>
+          <t>Speaker is not subordinate to anyone; he is the constitutional authority.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
+          <t>Which article provides for the privileges of Parliament members?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 108</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>He presides over joint sittings under Article 108.</t>
+          <t>This article grants MPs certain privileges and immunities.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which of the following is not a part of the Indian Parliament?</t>
+          <t>Which of the following is NOT a function of the Estimates Committee?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Suggesting economic improvements</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Examining estimates in Budget</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Examining CAG reports</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Ensuring efficient allocation</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Examining CAG reports</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>The Supreme Court is part of the Judiciary, not the Parliament.</t>
+          <t>That's the job of Public Accounts Committee, not Estimates Committee.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Who decides whether a bill is a Money Bill or not?</t>
+          <t>Which of the following is not a function of Parliament?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Executive appointments</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Amending Constitution</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>The Speaker’s decision on Money Bill is final under Article 110.</t>
+          <t>Judicial review is the function of courts, not Parliament.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Who decides whether a Bill is a Money Bill or not?</t>
+          <t>What is the current maximum strength of Rajya Sabha?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>245</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>238</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Speaker’s decision is final under Article 110.</t>
+          <t>Rajya Sabha can have up to 250 members, out of which 12 are nominated.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What is the current maximum strength of Rajya Sabha?</t>
+          <t>Which body examines the annual financial statement laid before Parliament?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Rajya Sabha can have up to 250 members, out of which 12 are nominated.</t>
+          <t>The Public Accounts Committee examines the audit reports and financial accounts.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Who can disqualify a Member of Parliament on grounds of defection?</t>
+          <t>Which Article deals with the procedure in financial matters like Budget?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 109</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Speaker or Chairman</t>
+          <t>Article 112</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Speaker or Chairman</t>
+          <t>Article 117</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>They decide disqualification under the 10th Schedule.</t>
+          <t>It governs financial bills other than money bills.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which of the following statements is true about Private Member’s Bill?</t>
+          <t>Who can introduce a Private Member Bill?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Introduced only by ministers</t>
+          <t>Only opposition MPs</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Introduced only in Lok Sabha</t>
+          <t>Any non-minister MP</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Introduced by any MP not a minister</t>
+          <t>Only ruling party MP</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Requires President’s assent first</t>
+          <t>Only nominated MPs</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Introduced by any MP not a minister</t>
+          <t>Any non-minister MP</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Private Members are MPs who are not part of the executive.</t>
+          <t>Private Member Bills are introduced by MPs who are not Ministers.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
+          <t>How many types of major parliamentary committees exist in India?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>The Vice President of India is the ex-officio Chairman of Rajya Sabha.</t>
+          <t>Standing and Ad-hoc are the two main types.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which motion is used to express disapproval of a specific policy of the government?</t>
+          <t>How many houses does the Indian Parliament consist of?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>No-confidence motion</t>
+          <t>One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Censure motion</t>
+          <t>Two</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>Three</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cut motion</t>
+          <t>Four</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Censure motion</t>
+          <t>Two</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>It expresses strong disapproval of a specific policy.</t>
+          <t>The Indian Parliament has two houses – Lok Sabha and Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Who decides whether a bill is a Money Bill or not?</t>
+          <t>The motion to remove the Vice President must be introduced in</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>President’s Office</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>As per Article 110, the Speaker's decision is final.</t>
+          <t>Removal motion of Vice President must originate in Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which House of Parliament has special powers regarding creation of All-India Services?</t>
+          <t>Which of the following is NOT a part of Parliament?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>Lok Sabha</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Rajya Sabha</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Chief Justice of India</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Rajya Sabha can pass a resolution to create All-India Services.</t>
+          <t>He is part of Judiciary, not Legislature.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which article provides for the privileges of Parliament members?</t>
+          <t>The Parliament can legislate on a subject in the State List if</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>Rajya Sabha passes a resolution</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Article 108</t>
+          <t>There is national emergency</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>States request it</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Article 105</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>This article grants MPs certain privileges and immunities.</t>
+          <t>All these are valid conditions under which Parliament can legislate on State subjects.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The power to summon or prorogue Parliament rests with</t>
+          <t>Which of the following motions can lead to the fall of the Council of Ministers?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Calling Attention Motion</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Adjournment Motion</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Censure Motion</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>No-confidence Motion</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>No-confidence Motion</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>President summons and prorogues the Parliament on advice of Council of Ministers.</t>
+          <t>It expresses loss of confidence in the government.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which of the following statements is true regarding Zero Hour?</t>
+          <t>Which of the following is not a function of Parliament?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>It is mentioned in Constitution</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>It starts at 11 AM</t>
+          <t>Amending the Constitution</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>It starts after lunch</t>
+          <t>Electing the President</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>It is a parliamentary convention</t>
+          <t>Enforcing laws</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>It is a parliamentary convention</t>
+          <t>Enforcing laws</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Zero Hour is not in the rulebook, it's a practice started in 1962.</t>
+          <t>Enforcing laws is the function of the executive.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which of the following is not a function of Parliament?</t>
+          <t>What is the tenure of the Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Executive appointments</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Till next election</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Amending Constitution</t>
+          <t>Till he/she resigns or removed</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Till he/she resigns or removed</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Judicial review is the function of courts, not Parliament.</t>
+          <t>Speaker holds office until removed or resignation, even after dissolution.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>What is the term of a Rajya Sabha member?</t>
+          <t>Which Article allows the Parliament to make laws on a matter in the State List under national interest?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>7 years</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Rajya Sabha members have a term of 6 years, with one-third retiring every two years.</t>
+          <t>Rajya Sabha can authorize Parliament to legislate on State List in national interest.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a part of Parliament?</t>
+          <t>What is the maximum time Rajya Sabha can hold a Money Bill?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>7 days</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>21 days</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>He is part of Judiciary, not Legislature.</t>
+          <t>Rajya Sabha must return a Money Bill within 14 days; else it is deemed passed.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Under normal circumstances, how many sessions of Parliament are held in a year?</t>
+          <t>Who can introduce an ordinary bill in Parliament?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Only Minister</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Only MP from ruling party</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Only Lok Sabha MP</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Budget, Monsoon, and Winter Sessions are held annually.</t>
+          <t>Ordinary Bills can be introduced by any MP.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Who presides over the joint sitting of Parliament?</t>
+          <t>In the event of a conflict between two Houses on an ordinary bill, the mechanism used is</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Money Bill clause</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>President’s Order</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Constitutional Amendment</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>In joint sittings, the Speaker of Lok Sabha presides.</t>
+          <t>Joint sitting is used to resolve deadlock on ordinary bills.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>In which schedule is the anti-defection law mentioned?</t>
+          <t>Can a non-member of Parliament become a minister?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>8th Schedule</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>9th Schedule</t>
+          <t>Yes, for 3 months</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>11th Schedule</t>
+          <t>Yes, for 1 year</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>The 10th Schedule was added by the 52nd Amendment for anti-defection.</t>
+          <t>He must get elected to either House within 6 months.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which of the following statements is true regarding the dissolution of Rajya Sabha?</t>
+          <t>What is the maximum number of members in Rajya Sabha from a single state?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>It is dissolved every 5 years</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>It is dissolved by the President</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>It is dissolved by the Prime Minister</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>It cannot be dissolved</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>It cannot be dissolved</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent house and is not subject to dissolution.</t>
+          <t>Uttar Pradesh sends the highest number (31) to Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The concept of Parliamentary Privileges in India is taken from which country?</t>
+          <t>A bill becomes a law only after it is signed by</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>India borrowed Parliamentary Privileges from the British system.</t>
+          <t>President’s assent is essential for a bill to become a law.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which of the following motions can lead to the fall of the Council of Ministers?</t>
+          <t>Which House is considered the Council of States?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Calling Attention Motion</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Adjournment Motion</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Censure Motion</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>No-confidence Motion</t>
-        </is>
-      </c>
+          <t>Vidhan Sabha</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>No-confidence Motion</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>It expresses loss of confidence in the government.</t>
+          <t>Rajya Sabha represents the states and is called the Council of States.</t>
         </is>
       </c>
     </row>
@@ -3376,287 +3384,283 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What is the quorum of Rajya Sabha?</t>
+          <t>Which House of Parliament has special powers regarding creation of All-India Services?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>15 members</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1/6th of total</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1/10th of total</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>50 members</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1/10th of total</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Minimum 1/10th of the total strength is required to conduct business.</t>
+          <t>Rajya Sabha can pass a resolution to create All-India Services.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The first hour of every parliamentary sitting is reserved for:</t>
+          <t>The first Lok Sabha was constituted in</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Adjournment motion</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Debate</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Question Hour</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Private member bill</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Question Hour</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>It is devoted to questions and answers.</t>
+          <t>The first Lok Sabha was formed in 1952 after the first general election.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>How many members can be nominated to the Rajya Sabha by the President?</t>
+          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>The President can nominate 12 members to Rajya Sabha from fields like art, science, etc.</t>
+          <t>He presides over joint sittings under Article 108.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>How many types of major parliamentary committees exist in India?</t>
+          <t>Which article empowers Parliament to create new states?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Article 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Article 1</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Article 5</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Standing and Ad-hoc are the two main types.</t>
+          <t>Parliament can form new states or alter existing ones.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The power to summon or prorogue the Parliament rests with?</t>
+          <t>Which House of Parliament is considered more powerful in terms of money matters?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>Lok Sabha</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Both equal</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Vice President</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>The President summons and prorogues Parliament sessions.</t>
+          <t>Money Bills can only be introduced and passed in the Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>In the event of a conflict between two Houses on an ordinary bill, the mechanism used is</t>
+          <t>Which of the following is true about Zero Hour?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Money Bill clause</t>
+          <t>It is mentioned in Constitution</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>It begins at 12 noon</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>President’s Order</t>
+          <t>It is a procedural motion</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Constitutional Amendment</t>
+          <t>It is started by Rajya Sabha</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>It begins at 12 noon</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Joint sitting is used to resolve deadlock on ordinary bills.</t>
+          <t>Zero Hour starts at 12 PM and is an Indian innovation (not in Constitution).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which of the following is true about Zero Hour?</t>
+          <t>The maximum strength of the Lok Sabha is</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>It is mentioned in Constitution</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>It begins at 12 noon</t>
+          <t>545</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>It is a procedural motion</t>
+          <t>552</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>It is started by Rajya Sabha</t>
+          <t>560</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>It begins at 12 noon</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Zero Hour starts at 12 PM and is an Indian innovation (not in Constitution).</t>
+          <t>According to Article 81, the Lok Sabha can have up to 552 members.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The maximum gap between two sessions of Parliament cannot be more than</t>
+          <t>What is the maximum gap allowed between two parliamentary sessions?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3671,14 +3675,14 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>5 months</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>6 months</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>1 year</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>6 months</t>
@@ -3686,7 +3690,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>According to the Constitution, there must not be a gap of more than 6 months.</t>
+          <t>Parliament must meet at least once every six months.</t>
         </is>
       </c>
     </row>
@@ -3732,1717 +3736,1713 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Can Rajya Sabha be dissolved?</t>
+          <t>Which of the following is NOT a type of bill in Indian Parliament?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Yes, every 6 years</t>
+          <t>Appropriation Bill</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Yes, every 5 years</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Yes, at the discretion of President</t>
+          <t>Judicial Bill</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Judicial Bill</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
+          <t>There’s no such category; only legislative, money, financial bills exist.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which article of the Constitution deals with the composition of the Parliament?</t>
+          <t>Which of the following statements is true regarding Zero Hour?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>It is mentioned in Constitution</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>It starts at 11 AM</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Article 81</t>
+          <t>It starts after lunch</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>It is a parliamentary convention</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Article 79</t>
+          <t>It is a parliamentary convention</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Article 79 defines the structure of the Indian Parliament.</t>
+          <t>Zero Hour is not in the rulebook, it's a practice started in 1962.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Money Bill can be introduced only in</t>
+          <t>Which of the following is not a parliamentary committee?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Committee on Petitions</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Money Bills can be introduced only in Lok Sabha, as per Article 110.</t>
+          <t>Cabinet Committees are executive, not parliamentary.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>What happens if there is a deadlock on a Constitutional Amendment Bill?</t>
+          <t>Which Article provides for the privileges of Parliament?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Joint Sitting is held</t>
+          <t>Article 104</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>President decides</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lok Sabha prevails</t>
+          <t>Article 106</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bill fails</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bill fails</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>There is no provision for joint sitting on Constitutional Amendments.</t>
+          <t>It provides for the powers, privileges and immunities of Parliament and its members.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Who can introduce a Private Member Bill?</t>
+          <t>Which of the following is not a part of the Indian Parliament?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Only opposition MPs</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Any non-minister MP</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Only ruling party MP</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Only nominated MPs</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Any non-minister MP</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Private Member Bills are introduced by MPs who are not Ministers.</t>
+          <t>The Supreme Court is part of the Judiciary, not the Parliament.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>What is the tenure of the Speaker of Lok Sabha?</t>
+          <t>Money Bill can be introduced only in</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Till next election</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Till he/she resigns or removed</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Till he/she resigns or removed</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Speaker holds office until removed or resignation, even after dissolution.</t>
+          <t>Money Bills can be introduced only in Lok Sabha, as per Article 110.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The first sitting of the Constituent Assembly took place in which year?</t>
+          <t>Which of the following motions is NOT related to financial matters?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>Cut Motion</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Adjournment Motion</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Appropriation Bill</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>Finance Bill</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>Adjournment Motion</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>The Constituent Assembly first met on 9 December 1946.</t>
+          <t>It is used to draw attention to urgent matters, not financial matters.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which of the following statements is correct regarding Money Bill?</t>
+          <t>Who decides whether a bill is a Money Bill or not?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>It needs approval of Rajya Sabha</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Rajya Sabha can reject it</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rajya Sabha can suggest amendments</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rajya Sabha can amend it</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rajya Sabha can suggest amendments</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Rajya Sabha can only suggest, not amend or reject it.</t>
+          <t>As per Article 110, the Speaker's decision is final.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Who is the ex-officio Chairman of Rajya Sabha?</t>
+          <t>What is the term of a Rajya Sabha member?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>7 years</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>As per Article 64, Vice President is ex-officio Chairman of Rajya Sabha.</t>
+          <t>Rajya Sabha members have a term of 6 years, with one-third retiring every two years.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>What is the maximum strength of the Lok Sabha as per the Constitution?</t>
+          <t>The first Speaker of Lok Sabha was</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>G V Mavalankar</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>M A Ayyangar</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>S Radhakrishnan</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>G V Mavalankar</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>As per Article 81, the maximum strength is 552 members.</t>
+          <t>He was the first Speaker of Lok Sabha after 1952 elections.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>What is the quorum to constitute a meeting of the Lok Sabha?</t>
+          <t>Which Article empowers the Parliament to make laws on State List during emergency?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1/2 of total members</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1/10 of total members</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1/5 of total members</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1/4 of total members</t>
+          <t>Article 248</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1/10 of total members</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Quorum is the minimum number of members required to hold a sitting.</t>
+          <t>Parliament can legislate on state subjects during National Emergency under Article 250.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which article of the Constitution defines a Money Bill?</t>
+          <t>How many members can be nominated to the Rajya Sabha by the President?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Article 112</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Article 113</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Article 117</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>This article gives the definition of a Money Bill.</t>
+          <t>The President can nominate 12 members to Rajya Sabha from fields like art, science, etc.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which Article allows the Parliament to make laws on a matter in the State List under national interest?</t>
+          <t>Which House of Parliament is not subject to dissolution?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Article 252</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Article 253</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Rajya Sabha can authorize Parliament to legislate on State List in national interest.</t>
+          <t>Rajya Sabha is a permanent House, not subject to dissolution.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which of the following statements is incorrect regarding the Speaker of Lok Sabha?</t>
+          <t>How many readings does a bill go through in the Parliament?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>He/she can vote in first instance</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>He/she is elected from among Lok Sabha members</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>He/she can disqualify a member under anti-defection law</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>He/she is subordinate to the President</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>He/she is subordinate to the President</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Speaker is not subordinate to anyone; he is the constitutional authority.</t>
+          <t>Each House of Parliament conducts 3 readings: introduction, consideration, and passing.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>What is the difference between adjournment and prorogation?</t>
+          <t>Who presides over the joint sitting of Parliament?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>No difference</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Adjournment by President, Prorogation by Speaker</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Adjournment is for a short period, Prorogation ends session</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Adjournment ends the House</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Adjournment is for a short period, Prorogation ends session</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Adjournment is temporary; prorogation ends a session.</t>
+          <t>In joint sittings, the Speaker of Lok Sabha presides.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>How many times can the President summon Parliament in a year at minimum?</t>
+          <t>Who presides over the joint sitting of both Houses of Parliament?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>There must be at least two sessions in a year as per Article 85.</t>
+          <t>The Speaker of the Lok Sabha presides over joint sittings.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What is the maximum time Rajya Sabha can hold a Money Bill?</t>
+          <t>The concept of Parliamentary Privileges in India is taken from which country?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>7 days</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>21 days</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>14 days</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Rajya Sabha must return a Money Bill within 14 days; else it is deemed passed.</t>
+          <t>India borrowed Parliamentary Privileges from the British system.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which House of Parliament is considered more powerful in terms of money matters?</t>
+          <t>Who decides whether a bill is a Money Bill or not?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Both equal</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Money Bills can only be introduced and passed in the Lok Sabha.</t>
+          <t>The Speaker’s decision on Money Bill is final under Article 110.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Which House of Parliament can initiate impeachment of the President?</t>
+          <t>Which Article empowers Parliament to create new states?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lok Sabha only</t>
+          <t>Article 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Rajya Sabha only</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Article 4</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>Article 5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Article 3</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Both Houses can initiate impeachment independently.</t>
+          <t>It gives Parliament power to create or alter state boundaries.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Which article empowers the Parliament to make laws on State List under certain circumstances?</t>
+          <t>How many times can the President summon Parliament in a year at minimum?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Article 263</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Article 312</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Under Article 249, Rajya Sabha can pass a resolution allowing Parliament to legislate on State List.</t>
+          <t>There must be at least two sessions in a year as per Article 85.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Can a non-member of Parliament become a minister?</t>
+          <t>In which year was the Anti-Defection Law added to the Constitution?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Yes, for 3 months</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Yes, for 1 year</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>He must get elected to either House within 6 months.</t>
+          <t>It was added through the 52nd Amendment in 1985.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Which is not required to pass a Constitutional Amendment Bill?</t>
+          <t>Which of the following is NOT true about Rajya Sabha?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Simple Majority</t>
+          <t>It is a permanent House</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Special Majority</t>
+          <t>It has equal powers with Lok Sabha on Money Bills</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ratification by States</t>
+          <t>It represents states</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>President's assent</t>
+          <t>It has 250 members</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Simple Majority</t>
+          <t>It has equal powers with Lok Sabha on Money Bills</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Most Constitutional Amendments require special majority, not simple majority.</t>
+          <t>Rajya Sabha has limited role in Money Bills.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>In case of a deadlock between the two Houses, the President can summon a joint sitting under which article?</t>
+          <t>Which authority decides the disqualification of MPs under anti-defection?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Article 108</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Article 111</t>
+          <t>Speaker/Chairman</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Article 112</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Article 108</t>
+          <t>Speaker/Chairman</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Joint sitting can be called to resolve deadlock between Houses.</t>
+          <t>The Presiding Officer decides under 10th Schedule.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Money Bills can be introduced only in which House?</t>
+          <t>The power to summon or prorogue the Parliament rests with?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Either House</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
+          <t>Vice President</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Only Lok Sabha can introduce a Money Bill as per Article 110.</t>
+          <t>The President summons and prorogues Parliament sessions.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Which of the following is not a function of Parliament?</t>
+          <t>Which House of Parliament can initiate impeachment of the President?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>Lok Sabha only</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Amending the Constitution</t>
+          <t>Rajya Sabha only</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Electing the President</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Enforcing laws</t>
+          <t>Joint Sitting</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Enforcing laws</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Enforcing laws is the function of the executive.</t>
+          <t>Both Houses can initiate impeachment independently.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which session of Parliament is usually held from February to May?</t>
+          <t>The power to summon or prorogue Parliament rests with</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Monsoon Session</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Winter Session</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Budget Session</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Special Session</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Budget Session</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>It usually begins in February and includes the budget presentation.</t>
+          <t>President summons and prorogues the Parliament on advice of Council of Ministers.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Can the Rajya Sabha be dissolved?</t>
+          <t>What is the tenure of the members of the Rajya Sabha?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Yes, after 6 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Yes, by the President</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Only in emergency</t>
+          <t>Till dissolved</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
+          <t>One-third members retire every 2 years.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Which of the following is NOT true about Rajya Sabha?</t>
+          <t>What is the maximum strength of the Lok Sabha as per the Constitution?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>It is a permanent House</t>
+          <t>530</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>It has equal powers with Lok Sabha on Money Bills</t>
+          <t>545</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>It represents states</t>
+          <t>552</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>It has 250 members</t>
+          <t>560</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>It has equal powers with Lok Sabha on Money Bills</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Rajya Sabha has limited role in Money Bills.</t>
+          <t>As per Article 81, the maximum strength is 552 members.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a function of Parliament?</t>
+          <t>Which schedule of the Constitution contains the Anti-Defection Law?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Law-making</t>
+          <t>7th</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Amending Constitution</t>
+          <t>8th</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Controlling Executive</t>
+          <t>9th</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Electing President</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Electing President</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>President is elected by an electoral college, not Parliament alone.</t>
+          <t>The Tenth Schedule deals with provisions regarding disqualification on the grounds of defection.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>How many members of Anglo-Indian community could be nominated to Lok Sabha (before 104th Amendment)?</t>
+          <t>Can Rajya Sabha be dissolved?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Yes, every 6 years</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Yes, every 5 years</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes, at the discretion of President</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Earlier, President could nominate 2 Anglo-Indians (now discontinued after 104th Amendment).</t>
+          <t>Rajya Sabha is a permanent body and cannot be dissolved.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which Article authorizes Parliament to make laws on State List during national emergency?</t>
+          <t>Which is not required to pass a Constitutional Amendment Bill?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>Simple Majority</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Special Majority</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Ratification by States</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>President's assent</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Simple Majority</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>During National Emergency, Parliament can legislate on State subjects under Article 250.</t>
+          <t>Most Constitutional Amendments require special majority, not simple majority.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>In which year was the Parliament House of India inaugurated?</t>
+          <t>Which Schedule of the Constitution contains provisions relating to disqualification on the grounds of defection?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>9th Schedule</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>12th Schedule</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>The current Parliament House was inaugurated in 1927 by Lord Irwin.</t>
+          <t>10th Schedule deals with anti-defection law as added by the 52nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>The motion to remove the Vice President must be introduced in</t>
+          <t>Which constitutional amendment lowered the voting age from 21 to 18?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>42nd</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Joint Sitting</t>
+          <t>44th</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>President’s Office</t>
+          <t>61st</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>52nd</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>61st</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Removal motion of Vice President must originate in Rajya Sabha.</t>
+          <t>The 61st Amendment Act, 1989, reduced the voting age.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>What is the minimum age to become a member of Rajya Sabha?</t>
+          <t>Who acts as the pro tem Speaker of Lok Sabha?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>25 years</t>
+          <t>Longest-serving MP</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>30 years</t>
+          <t>Senior-most member</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>35 years</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>21 years</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>30 years</t>
+          <t>Senior-most member</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>A candidate must be at least 30 years old to be elected to Rajya Sabha.</t>
+          <t>The senior-most member is appointed to conduct the first meeting until Speaker is elected.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>How many houses does the Indian Parliament consist of?</t>
+          <t>Which Committee examines the report of the Comptroller and Auditor General (CAG)?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>One</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Two</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Three</t>
+          <t>Privileges Committee</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Four</t>
+          <t>Business Advisory Committee</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Two</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>The Indian Parliament has two houses – Lok Sabha and Rajya Sabha.</t>
+          <t>PAC examines CAG reports and ensures public money is spent properly.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>What is the maximum tenure of Lok Sabha?</t>
+          <t>The quorum for a meeting of either House of Parliament is?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3 years</t>
+          <t>1/5th</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>1/4th</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>1/6th</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>1/10th</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>1/10th</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Lok Sabha has a normal term of 5 years unless dissolved earlier.</t>
+          <t>The minimum number of members required to hold a meeting is 1/10th of the total strength.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Which House has more power in the case of a Money Bill?</t>
+          <t>What is the maximum time limit within which Parliament must approve a Money Bill after it is introduced?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Both equal</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+          <t>75 days</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Rajya Sabha can only make recommendations on Money Bills.</t>
+          <t>Money Bill must be passed within 14 days by both Houses.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Which provision ensures that Parliament remains sovereign in making laws?</t>
+          <t>Who can disqualify a Member of Parliament on grounds of defection?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Doctrine of pith and substance</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Basic structure</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>Speaker or Chairman</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Doctrine of pith and substance</t>
+          <t>Speaker or Chairman</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>It gives Parliament flexibility in legislative matters.</t>
+          <t>They decide disqualification under the 10th Schedule.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>The maximum strength of the Lok Sabha is</t>
+          <t>Under which article can Parliament punish a person for breach of privilege?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>Article 107</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>Article 118</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>Article 105</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>According to Article 81, the Lok Sabha can have up to 552 members.</t>
+          <t>It includes the powers and privileges of Parliament members.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which Article mentions the composition of the Rajya Sabha?</t>
+          <t>Which Article authorizes Parliament to make laws on State List during national emergency?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Article 81</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Article 82</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Article 83</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Article 80 of the Constitution deals with the composition of Rajya Sabha.</t>
+          <t>During National Emergency, Parliament can legislate on State subjects under Article 250.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Which article empowers Parliament to create new states?</t>
+          <t>Who can introduce a bill for Constitutional Amendment?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Article 2</t>
+          <t>Only Ministers</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>Only Lok Sabha MP</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Article 1</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Article 5</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Article 3</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Parliament can form new states or alter existing ones.</t>
+          <t>Both Ministers and private members can introduce Constitutional Amendments.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Who is the custodian of the Lok Sabha?</t>
+          <t>What is the quorum to conduct a sitting of either House of Parliament?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>1/5th of total membership</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>1/10th of total membership</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>1/3rd of total membership</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Half the total strength</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>1/10th of total membership</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>The Speaker is the guardian and controller of Lok Sabha.</t>
+          <t>Quorum is 1/10th of total strength of the House.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which committee is called the “watchdog of public purse”?</t>
+          <t>The first sitting of the Constituent Assembly took place in which year?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Committee on Subordinate Legislation</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Committee on Public Undertakings</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>It ensures accountability in public spending.</t>
+          <t>The Constituent Assembly first met on 9 December 1946.</t>
         </is>
       </c>
     </row>
